--- a/Survey_data_real.xlsx
+++ b/Survey_data_real.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop (1)\Other\ShinyAPPnorway\ACCESS-FjordAPP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78F939EC-2B1D-4360-8C6D-150DDBB76291}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{759910D6-C3B7-4568-B3DF-B66AC32EA9B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-4800" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="89">
   <si>
     <t>Date</t>
   </si>
@@ -2186,6 +2186,9 @@
       <c r="G64">
         <v>867</v>
       </c>
+      <c r="H64" t="s">
+        <v>8</v>
+      </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:H998">

--- a/Survey_data_real.xlsx
+++ b/Survey_data_real.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop (1)\Other\ShinyAPPnorway\ACCESS-FjordAPP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{759910D6-C3B7-4568-B3DF-B66AC32EA9B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CDDF252-07A5-4B16-BEE9-994ED5C6BE9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-4800" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="catchdata" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="97">
   <si>
     <t>Date</t>
   </si>
@@ -304,6 +304,30 @@
   </si>
   <si>
     <t>topwater</t>
+  </si>
+  <si>
+    <t>Prestmåsøya est</t>
+  </si>
+  <si>
+    <t>Rørstad</t>
+  </si>
+  <si>
+    <t>Elvkroken</t>
+  </si>
+  <si>
+    <t>almost halibut (2)</t>
+  </si>
+  <si>
+    <t>alti_liveli</t>
+  </si>
+  <si>
+    <t>fishing_biodiversity</t>
+  </si>
+  <si>
+    <t>enrico.e.armelloni</t>
+  </si>
+  <si>
+    <t>bait fish</t>
   </si>
 </sst>
 </file>
@@ -675,7 +699,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I64"/>
+  <dimension ref="A1:I81"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="25.7265625" style="2" customWidth="1"/>
@@ -2188,6 +2212,379 @@
       </c>
       <c r="H64" t="s">
         <v>8</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A65" s="2">
+        <v>46172</v>
+      </c>
+      <c r="B65" t="s">
+        <v>89</v>
+      </c>
+      <c r="C65" t="s">
+        <v>93</v>
+      </c>
+      <c r="D65" t="s">
+        <v>40</v>
+      </c>
+      <c r="E65" t="s">
+        <v>83</v>
+      </c>
+      <c r="F65">
+        <v>45</v>
+      </c>
+      <c r="G65">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A66" s="2">
+        <v>46172</v>
+      </c>
+      <c r="B66" t="s">
+        <v>89</v>
+      </c>
+      <c r="C66" t="s">
+        <v>93</v>
+      </c>
+      <c r="D66" t="s">
+        <v>40</v>
+      </c>
+      <c r="E66" t="s">
+        <v>83</v>
+      </c>
+      <c r="F66">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A67" s="2">
+        <v>46172</v>
+      </c>
+      <c r="B67" t="s">
+        <v>89</v>
+      </c>
+      <c r="C67" t="s">
+        <v>95</v>
+      </c>
+      <c r="D67" t="s">
+        <v>40</v>
+      </c>
+      <c r="E67" t="s">
+        <v>83</v>
+      </c>
+      <c r="F67">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A68" s="2">
+        <v>46172</v>
+      </c>
+      <c r="B68" t="s">
+        <v>89</v>
+      </c>
+      <c r="C68" t="s">
+        <v>95</v>
+      </c>
+      <c r="D68" t="s">
+        <v>40</v>
+      </c>
+      <c r="E68" t="s">
+        <v>83</v>
+      </c>
+      <c r="F68">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A69" s="2">
+        <v>46172</v>
+      </c>
+      <c r="B69" t="s">
+        <v>89</v>
+      </c>
+      <c r="C69" t="s">
+        <v>95</v>
+      </c>
+      <c r="D69" t="s">
+        <v>40</v>
+      </c>
+      <c r="E69" t="s">
+        <v>83</v>
+      </c>
+      <c r="F69">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A70" s="2">
+        <v>46172</v>
+      </c>
+      <c r="B70" t="s">
+        <v>89</v>
+      </c>
+      <c r="C70" t="s">
+        <v>93</v>
+      </c>
+      <c r="D70" t="s">
+        <v>40</v>
+      </c>
+      <c r="E70" t="s">
+        <v>6</v>
+      </c>
+      <c r="F70">
+        <v>45</v>
+      </c>
+      <c r="H70" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A71" s="2">
+        <v>46172</v>
+      </c>
+      <c r="B71" t="s">
+        <v>89</v>
+      </c>
+      <c r="C71" t="s">
+        <v>86</v>
+      </c>
+      <c r="D71" t="s">
+        <v>41</v>
+      </c>
+      <c r="E71" t="s">
+        <v>6</v>
+      </c>
+      <c r="F71">
+        <v>43</v>
+      </c>
+      <c r="H71" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A72" s="2">
+        <v>46172</v>
+      </c>
+      <c r="B72" t="s">
+        <v>89</v>
+      </c>
+      <c r="C72" t="s">
+        <v>94</v>
+      </c>
+      <c r="D72" t="s">
+        <v>41</v>
+      </c>
+      <c r="E72" t="s">
+        <v>6</v>
+      </c>
+      <c r="F72">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A73" s="2">
+        <v>46172</v>
+      </c>
+      <c r="B73" t="s">
+        <v>89</v>
+      </c>
+      <c r="C73" t="s">
+        <v>85</v>
+      </c>
+      <c r="D73" t="s">
+        <v>40</v>
+      </c>
+      <c r="E73" t="s">
+        <v>6</v>
+      </c>
+      <c r="F73">
+        <v>70</v>
+      </c>
+      <c r="G73">
+        <v>3400</v>
+      </c>
+      <c r="H73" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A74" s="2">
+        <v>46172</v>
+      </c>
+      <c r="B74" t="s">
+        <v>90</v>
+      </c>
+      <c r="C74" t="s">
+        <v>94</v>
+      </c>
+      <c r="D74" t="s">
+        <v>41</v>
+      </c>
+      <c r="E74" t="s">
+        <v>6</v>
+      </c>
+      <c r="F74">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A75" s="2">
+        <v>46172</v>
+      </c>
+      <c r="B75" t="s">
+        <v>90</v>
+      </c>
+      <c r="C75" t="s">
+        <v>94</v>
+      </c>
+      <c r="D75" t="s">
+        <v>41</v>
+      </c>
+      <c r="E75" t="s">
+        <v>6</v>
+      </c>
+      <c r="F75">
+        <v>75</v>
+      </c>
+      <c r="G75">
+        <v>4600</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A76" s="2">
+        <v>46172</v>
+      </c>
+      <c r="B76" t="s">
+        <v>44</v>
+      </c>
+      <c r="C76" t="s">
+        <v>95</v>
+      </c>
+      <c r="D76" t="s">
+        <v>41</v>
+      </c>
+      <c r="E76" t="s">
+        <v>6</v>
+      </c>
+      <c r="F76">
+        <v>55</v>
+      </c>
+      <c r="G76">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A77" s="2">
+        <v>46173</v>
+      </c>
+      <c r="B77" t="s">
+        <v>44</v>
+      </c>
+      <c r="C77" t="s">
+        <v>94</v>
+      </c>
+      <c r="D77" t="s">
+        <v>41</v>
+      </c>
+      <c r="E77" t="s">
+        <v>6</v>
+      </c>
+      <c r="F77">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A78" s="2">
+        <v>46173</v>
+      </c>
+      <c r="B78" t="s">
+        <v>44</v>
+      </c>
+      <c r="C78" t="s">
+        <v>94</v>
+      </c>
+      <c r="D78" t="s">
+        <v>96</v>
+      </c>
+      <c r="E78" t="s">
+        <v>68</v>
+      </c>
+      <c r="F78">
+        <v>104</v>
+      </c>
+      <c r="G78">
+        <v>13000</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A79" s="2">
+        <v>46173</v>
+      </c>
+      <c r="B79" t="s">
+        <v>54</v>
+      </c>
+      <c r="C79" t="s">
+        <v>93</v>
+      </c>
+      <c r="D79" t="s">
+        <v>60</v>
+      </c>
+      <c r="E79" t="s">
+        <v>52</v>
+      </c>
+      <c r="F79">
+        <v>35</v>
+      </c>
+      <c r="H79" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A80" s="2">
+        <v>46173</v>
+      </c>
+      <c r="B80" t="s">
+        <v>91</v>
+      </c>
+      <c r="C80" t="s">
+        <v>95</v>
+      </c>
+      <c r="D80" t="s">
+        <v>41</v>
+      </c>
+      <c r="E80" t="s">
+        <v>79</v>
+      </c>
+      <c r="F80">
+        <v>68</v>
+      </c>
+      <c r="G80">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A81" s="2">
+        <v>46173</v>
+      </c>
+      <c r="B81" t="s">
+        <v>42</v>
+      </c>
+      <c r="C81" t="s">
+        <v>93</v>
+      </c>
+      <c r="D81" t="s">
+        <v>60</v>
+      </c>
+      <c r="E81" t="s">
+        <v>52</v>
+      </c>
+      <c r="F81">
+        <v>68</v>
+      </c>
+      <c r="G81">
+        <v>1500</v>
       </c>
     </row>
   </sheetData>
@@ -3039,7 +3436,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>42</v>
       </c>
@@ -3086,7 +3483,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>42</v>
       </c>
@@ -3136,7 +3533,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>44</v>
       </c>
@@ -3186,7 +3583,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>42</v>
       </c>
@@ -3236,7 +3633,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>42</v>
       </c>
@@ -3286,7 +3683,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>42</v>
       </c>
@@ -3336,52 +3733,388 @@
         <v>56</v>
       </c>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="C23" s="4"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="C24" s="4"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="C25" s="4"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-    </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="C26" s="4"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
-    </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="C27" s="4"/>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
-    </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="C28" s="4"/>
-      <c r="D28" s="3"/>
-      <c r="E28" s="3"/>
-    </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="C29" s="4"/>
-      <c r="D29" s="3"/>
-      <c r="E29" s="3"/>
-    </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>89</v>
+      </c>
+      <c r="B23" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="2">
+        <v>46172</v>
+      </c>
+      <c r="D23" s="3">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="E23" s="3">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="F23" s="6">
+        <v>67.368099999999998</v>
+      </c>
+      <c r="G23" s="6">
+        <v>15.1264</v>
+      </c>
+      <c r="H23" s="6">
+        <v>67.368099999999998</v>
+      </c>
+      <c r="I23" s="6">
+        <v>15.1264</v>
+      </c>
+      <c r="J23" s="6">
+        <v>4</v>
+      </c>
+      <c r="K23" s="6">
+        <v>13</v>
+      </c>
+      <c r="L23" s="6">
+        <v>30</v>
+      </c>
+      <c r="O23" t="s">
+        <v>36</v>
+      </c>
+      <c r="P23">
+        <v>240</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>38</v>
+      </c>
+      <c r="R23" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>90</v>
+      </c>
+      <c r="B24" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="2">
+        <v>46172</v>
+      </c>
+      <c r="D24" s="3">
+        <v>0.60416666666666663</v>
+      </c>
+      <c r="E24" s="3">
+        <v>0.625</v>
+      </c>
+      <c r="F24" s="6">
+        <v>67.349299999999999</v>
+      </c>
+      <c r="G24" s="6">
+        <v>15.1318</v>
+      </c>
+      <c r="H24" s="6">
+        <v>67.349299999999999</v>
+      </c>
+      <c r="I24" s="6">
+        <v>15.1318</v>
+      </c>
+      <c r="J24" s="6">
+        <v>4</v>
+      </c>
+      <c r="K24" s="6">
+        <v>15</v>
+      </c>
+      <c r="L24" s="6">
+        <v>40</v>
+      </c>
+      <c r="M24" s="6">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="N24" s="6">
+        <v>22.9</v>
+      </c>
+      <c r="O24" t="s">
+        <v>55</v>
+      </c>
+      <c r="P24" s="6">
+        <v>210</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>38</v>
+      </c>
+      <c r="R24" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>44</v>
+      </c>
+      <c r="B25" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="2">
+        <v>46172</v>
+      </c>
+      <c r="D25" s="3">
+        <v>0.63888888888888884</v>
+      </c>
+      <c r="E25" s="3">
+        <v>0.67708333333333337</v>
+      </c>
+      <c r="F25" s="6">
+        <v>67.503900000000002</v>
+      </c>
+      <c r="G25" s="6">
+        <v>15.3994</v>
+      </c>
+      <c r="H25" s="6">
+        <v>67.503900000000002</v>
+      </c>
+      <c r="I25" s="6">
+        <v>15.3994</v>
+      </c>
+      <c r="J25" s="6">
+        <v>4</v>
+      </c>
+      <c r="K25" s="6">
+        <v>10</v>
+      </c>
+      <c r="L25" s="6">
+        <v>50</v>
+      </c>
+      <c r="O25" t="s">
+        <v>55</v>
+      </c>
+      <c r="P25" s="6">
+        <v>160</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>38</v>
+      </c>
+      <c r="R25" t="s">
+        <v>56</v>
+      </c>
+      <c r="S25" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>44</v>
+      </c>
+      <c r="B26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="2">
+        <v>46173</v>
+      </c>
+      <c r="D26" s="3">
+        <v>0.52083333333333337</v>
+      </c>
+      <c r="E26" s="3">
+        <v>0.56944444444444442</v>
+      </c>
+      <c r="F26" s="6">
+        <v>67.503900000000002</v>
+      </c>
+      <c r="G26" s="6">
+        <v>15.3994</v>
+      </c>
+      <c r="H26" s="6">
+        <v>67.503900000000002</v>
+      </c>
+      <c r="I26" s="6">
+        <v>15.3994</v>
+      </c>
+      <c r="J26" s="6">
+        <v>4</v>
+      </c>
+      <c r="K26" s="6">
+        <v>10</v>
+      </c>
+      <c r="L26" s="6">
+        <v>50</v>
+      </c>
+      <c r="M26" s="6">
+        <v>10</v>
+      </c>
+      <c r="N26" s="6">
+        <v>28</v>
+      </c>
+      <c r="O26" t="s">
+        <v>37</v>
+      </c>
+      <c r="P26" s="6">
+        <v>250</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>38</v>
+      </c>
+      <c r="R26" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>54</v>
+      </c>
+      <c r="B27" t="s">
+        <v>53</v>
+      </c>
+      <c r="C27" s="2">
+        <v>46173</v>
+      </c>
+      <c r="D27" s="3">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="E27" s="3">
+        <v>0.69791666666666663</v>
+      </c>
+      <c r="F27" s="6">
+        <v>67.5792</v>
+      </c>
+      <c r="G27" s="6">
+        <v>15.7844</v>
+      </c>
+      <c r="H27" s="7">
+        <v>67.5792</v>
+      </c>
+      <c r="I27" s="6">
+        <v>15.7844</v>
+      </c>
+      <c r="J27" s="6">
+        <v>3</v>
+      </c>
+      <c r="K27">
+        <v>20</v>
+      </c>
+      <c r="L27">
+        <v>40</v>
+      </c>
+      <c r="O27" t="s">
+        <v>55</v>
+      </c>
+      <c r="P27" s="6">
+        <v>170</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>38</v>
+      </c>
+      <c r="R27" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>91</v>
+      </c>
+      <c r="B28" t="s">
+        <v>53</v>
+      </c>
+      <c r="C28" s="2">
+        <v>46173</v>
+      </c>
+      <c r="D28" s="3">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="E28" s="3">
+        <v>0.8125</v>
+      </c>
+      <c r="F28" s="6">
+        <v>67.353300000000004</v>
+      </c>
+      <c r="G28" s="6">
+        <v>15.5144</v>
+      </c>
+      <c r="H28" s="6">
+        <v>67.353300000000004</v>
+      </c>
+      <c r="I28" s="6">
+        <v>15.5144</v>
+      </c>
+      <c r="J28" s="6">
+        <v>4</v>
+      </c>
+      <c r="K28" s="6">
+        <v>10</v>
+      </c>
+      <c r="L28" s="6">
+        <v>30</v>
+      </c>
+      <c r="O28" t="s">
+        <v>55</v>
+      </c>
+      <c r="P28" s="6">
+        <v>60</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>38</v>
+      </c>
+      <c r="R28" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>42</v>
+      </c>
+      <c r="B29" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="2">
+        <v>46175</v>
+      </c>
+      <c r="D29" s="3">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="F29" s="6">
+        <v>67.516000000000005</v>
+      </c>
+      <c r="G29" s="6">
+        <v>15.481199999999999</v>
+      </c>
+      <c r="H29" s="6">
+        <v>67.516000000000005</v>
+      </c>
+      <c r="I29" s="6">
+        <v>15.481199999999999</v>
+      </c>
+      <c r="J29" s="6">
+        <v>3</v>
+      </c>
+      <c r="K29" s="6">
+        <v>50</v>
+      </c>
+      <c r="L29" s="6">
+        <v>70</v>
+      </c>
+      <c r="M29" s="6">
+        <v>10</v>
+      </c>
+      <c r="N29" s="6">
+        <v>28</v>
+      </c>
+      <c r="O29" t="s">
+        <v>36</v>
+      </c>
+      <c r="P29" s="6">
+        <v>157</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>38</v>
+      </c>
+      <c r="R29" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.35">
       <c r="C30" s="4"/>
       <c r="D30" s="3"/>
       <c r="E30" s="3"/>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.35">
       <c r="C31" s="4"/>
       <c r="D31" s="3"/>
       <c r="E31" s="3"/>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.35">
       <c r="C32" s="4"/>
       <c r="D32" s="3"/>
       <c r="E32" s="3"/>

--- a/Survey_data_real.xlsx
+++ b/Survey_data_real.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop (1)\Other\ShinyAPPnorway\ACCESS-FjordAPP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CDDF252-07A5-4B16-BEE9-994ED5C6BE9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE680AB4-F6EA-4EE6-8E68-F2B8A9F493FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="717" uniqueCount="110">
   <si>
     <t>Date</t>
   </si>
@@ -328,6 +328,45 @@
   </si>
   <si>
     <t>bait fish</t>
+  </si>
+  <si>
+    <t>Berrflogan tunnel</t>
+  </si>
+  <si>
+    <t>Faerøyvalen</t>
+  </si>
+  <si>
+    <t>Rain</t>
+  </si>
+  <si>
+    <t>vedmannen</t>
+  </si>
+  <si>
+    <t>fermati01</t>
+  </si>
+  <si>
+    <t>francimazzieri</t>
+  </si>
+  <si>
+    <t>Mackerel</t>
+  </si>
+  <si>
+    <t>Filippo</t>
+  </si>
+  <si>
+    <t>Marco</t>
+  </si>
+  <si>
+    <t>empty (female)</t>
+  </si>
+  <si>
+    <t>seaquirt?</t>
+  </si>
+  <si>
+    <t>fish rest</t>
+  </si>
+  <si>
+    <t>small crab</t>
   </si>
 </sst>
 </file>
@@ -340,7 +379,7 @@
     <numFmt numFmtId="166" formatCode="#,##0.0000"/>
     <numFmt numFmtId="167" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -358,6 +397,12 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -383,7 +428,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -395,6 +440,10 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -699,7 +748,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I81"/>
+  <dimension ref="A1:I118"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="25.7265625" style="2" customWidth="1"/>
@@ -707,6 +756,7 @@
     <col min="3" max="3" width="21" customWidth="1"/>
     <col min="4" max="4" width="13.7265625" customWidth="1"/>
     <col min="5" max="5" width="19.1796875" customWidth="1"/>
+    <col min="9" max="9" width="17.6328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.35">
@@ -2564,11 +2614,11 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A81" s="2">
         <v>46173</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B81" s="10" t="s">
         <v>42</v>
       </c>
       <c r="C81" t="s">
@@ -2585,6 +2635,836 @@
       </c>
       <c r="G81">
         <v>1500</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A82" s="2">
+        <v>46187</v>
+      </c>
+      <c r="B82" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="C82" t="s">
+        <v>86</v>
+      </c>
+      <c r="D82" t="s">
+        <v>60</v>
+      </c>
+      <c r="E82" t="s">
+        <v>52</v>
+      </c>
+      <c r="F82">
+        <v>80</v>
+      </c>
+      <c r="G82">
+        <v>3150</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A83" s="2">
+        <v>46187</v>
+      </c>
+      <c r="B83" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="C83" t="s">
+        <v>86</v>
+      </c>
+      <c r="D83" t="s">
+        <v>60</v>
+      </c>
+      <c r="E83" t="s">
+        <v>61</v>
+      </c>
+      <c r="F83">
+        <v>74</v>
+      </c>
+      <c r="G83">
+        <v>4400</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A84" s="2">
+        <v>46187</v>
+      </c>
+      <c r="B84" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="C84" t="s">
+        <v>86</v>
+      </c>
+      <c r="D84" t="s">
+        <v>60</v>
+      </c>
+      <c r="E84" t="s">
+        <v>61</v>
+      </c>
+      <c r="F84">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A85" s="2">
+        <v>46200</v>
+      </c>
+      <c r="B85" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="C85" t="s">
+        <v>100</v>
+      </c>
+      <c r="D85" t="s">
+        <v>60</v>
+      </c>
+      <c r="E85" t="s">
+        <v>6</v>
+      </c>
+      <c r="F85">
+        <v>56</v>
+      </c>
+      <c r="G85">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A86" s="2">
+        <v>46200</v>
+      </c>
+      <c r="B86" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="C86" t="s">
+        <v>100</v>
+      </c>
+      <c r="D86" t="s">
+        <v>40</v>
+      </c>
+      <c r="E86" t="s">
+        <v>79</v>
+      </c>
+      <c r="F86">
+        <v>54</v>
+      </c>
+      <c r="G86">
+        <v>1650</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A87" s="2">
+        <v>46200</v>
+      </c>
+      <c r="B87" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="C87" t="s">
+        <v>86</v>
+      </c>
+      <c r="D87" t="s">
+        <v>60</v>
+      </c>
+      <c r="E87" t="s">
+        <v>6</v>
+      </c>
+      <c r="F87">
+        <v>54</v>
+      </c>
+      <c r="G87">
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A88" s="2">
+        <v>46200</v>
+      </c>
+      <c r="B88" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="C88" t="s">
+        <v>86</v>
+      </c>
+      <c r="D88" t="s">
+        <v>60</v>
+      </c>
+      <c r="E88" t="s">
+        <v>52</v>
+      </c>
+      <c r="F88">
+        <v>48</v>
+      </c>
+      <c r="G88">
+        <v>465</v>
+      </c>
+      <c r="H88" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A89" s="2">
+        <v>46210</v>
+      </c>
+      <c r="B89" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C89" t="s">
+        <v>86</v>
+      </c>
+      <c r="D89" t="s">
+        <v>60</v>
+      </c>
+      <c r="E89" t="s">
+        <v>6</v>
+      </c>
+      <c r="F89">
+        <v>95</v>
+      </c>
+      <c r="G89">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A90" s="2">
+        <v>46210</v>
+      </c>
+      <c r="B90" t="s">
+        <v>44</v>
+      </c>
+      <c r="C90" t="s">
+        <v>86</v>
+      </c>
+      <c r="D90" t="s">
+        <v>41</v>
+      </c>
+      <c r="E90" t="s">
+        <v>6</v>
+      </c>
+      <c r="F90">
+        <v>84.5</v>
+      </c>
+      <c r="G90">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A91" s="2">
+        <v>46210</v>
+      </c>
+      <c r="B91" t="s">
+        <v>44</v>
+      </c>
+      <c r="C91" t="s">
+        <v>86</v>
+      </c>
+      <c r="D91" t="s">
+        <v>41</v>
+      </c>
+      <c r="E91" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A92" s="2">
+        <v>46223</v>
+      </c>
+      <c r="B92" t="s">
+        <v>42</v>
+      </c>
+      <c r="C92" t="s">
+        <v>101</v>
+      </c>
+      <c r="D92" t="s">
+        <v>41</v>
+      </c>
+      <c r="E92" t="s">
+        <v>6</v>
+      </c>
+      <c r="F92">
+        <v>82</v>
+      </c>
+      <c r="G92">
+        <v>4400</v>
+      </c>
+      <c r="I92" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A93" s="2">
+        <v>46223</v>
+      </c>
+      <c r="B93" t="s">
+        <v>42</v>
+      </c>
+      <c r="C93" t="s">
+        <v>101</v>
+      </c>
+      <c r="D93" t="s">
+        <v>41</v>
+      </c>
+      <c r="E93" t="s">
+        <v>52</v>
+      </c>
+      <c r="F93">
+        <v>55</v>
+      </c>
+      <c r="G93">
+        <v>700</v>
+      </c>
+      <c r="H93" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A94" s="2">
+        <v>46223</v>
+      </c>
+      <c r="B94" t="s">
+        <v>44</v>
+      </c>
+      <c r="C94" t="s">
+        <v>85</v>
+      </c>
+      <c r="D94" t="s">
+        <v>40</v>
+      </c>
+      <c r="E94" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A95" s="2">
+        <v>46223</v>
+      </c>
+      <c r="B95" t="s">
+        <v>44</v>
+      </c>
+      <c r="C95" t="s">
+        <v>85</v>
+      </c>
+      <c r="D95" t="s">
+        <v>40</v>
+      </c>
+      <c r="E95" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A96" s="2">
+        <v>46223</v>
+      </c>
+      <c r="B96" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="C96" t="s">
+        <v>102</v>
+      </c>
+      <c r="D96" t="s">
+        <v>40</v>
+      </c>
+      <c r="E96" t="s">
+        <v>83</v>
+      </c>
+      <c r="F96">
+        <v>54</v>
+      </c>
+      <c r="G96">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A97" s="2">
+        <v>46223</v>
+      </c>
+      <c r="B97" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="C97" t="s">
+        <v>86</v>
+      </c>
+      <c r="D97" t="s">
+        <v>40</v>
+      </c>
+      <c r="E97" t="s">
+        <v>6</v>
+      </c>
+      <c r="F97">
+        <v>87</v>
+      </c>
+      <c r="G97">
+        <v>5800</v>
+      </c>
+      <c r="I97" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A98" s="2">
+        <v>46223</v>
+      </c>
+      <c r="B98" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="C98" t="s">
+        <v>101</v>
+      </c>
+      <c r="D98" t="s">
+        <v>40</v>
+      </c>
+      <c r="E98" t="s">
+        <v>6</v>
+      </c>
+      <c r="F98">
+        <v>73</v>
+      </c>
+      <c r="G98">
+        <v>3900</v>
+      </c>
+      <c r="H98" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A99" s="2">
+        <v>46223</v>
+      </c>
+      <c r="B99" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="C99" t="s">
+        <v>101</v>
+      </c>
+      <c r="D99" t="s">
+        <v>40</v>
+      </c>
+      <c r="E99" t="s">
+        <v>83</v>
+      </c>
+      <c r="F99">
+        <v>53</v>
+      </c>
+      <c r="G99">
+        <v>1060</v>
+      </c>
+      <c r="I99" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A100" s="2">
+        <v>46227</v>
+      </c>
+      <c r="B100" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C100" t="s">
+        <v>105</v>
+      </c>
+      <c r="D100" t="s">
+        <v>41</v>
+      </c>
+      <c r="E100" t="s">
+        <v>83</v>
+      </c>
+      <c r="F100">
+        <v>35</v>
+      </c>
+      <c r="G100">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A101" s="2">
+        <v>46227</v>
+      </c>
+      <c r="B101" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C101" t="s">
+        <v>105</v>
+      </c>
+      <c r="D101" t="s">
+        <v>41</v>
+      </c>
+      <c r="E101" t="s">
+        <v>83</v>
+      </c>
+      <c r="F101">
+        <v>32</v>
+      </c>
+      <c r="G101">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A102" s="2">
+        <v>46227</v>
+      </c>
+      <c r="B102" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C102" t="s">
+        <v>105</v>
+      </c>
+      <c r="D102" t="s">
+        <v>41</v>
+      </c>
+      <c r="E102" t="s">
+        <v>83</v>
+      </c>
+      <c r="F102">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A103" s="2">
+        <v>46227</v>
+      </c>
+      <c r="B103" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C103" t="s">
+        <v>105</v>
+      </c>
+      <c r="D103" t="s">
+        <v>41</v>
+      </c>
+      <c r="E103" t="s">
+        <v>83</v>
+      </c>
+      <c r="F103">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A104" s="2">
+        <v>46227</v>
+      </c>
+      <c r="B104" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C104" t="s">
+        <v>105</v>
+      </c>
+      <c r="D104" t="s">
+        <v>41</v>
+      </c>
+      <c r="E104" t="s">
+        <v>83</v>
+      </c>
+      <c r="F104">
+        <v>38</v>
+      </c>
+      <c r="G104">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A105" s="2">
+        <v>46227</v>
+      </c>
+      <c r="B105" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C105" t="s">
+        <v>105</v>
+      </c>
+      <c r="D105" t="s">
+        <v>41</v>
+      </c>
+      <c r="E105" t="s">
+        <v>83</v>
+      </c>
+      <c r="F105">
+        <v>37</v>
+      </c>
+      <c r="G105">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A106" s="2">
+        <v>46227</v>
+      </c>
+      <c r="B106" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C106" t="s">
+        <v>105</v>
+      </c>
+      <c r="D106" t="s">
+        <v>41</v>
+      </c>
+      <c r="E106" t="s">
+        <v>83</v>
+      </c>
+      <c r="H106" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A107" s="2">
+        <v>46227</v>
+      </c>
+      <c r="B107" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C107" t="s">
+        <v>105</v>
+      </c>
+      <c r="D107" t="s">
+        <v>41</v>
+      </c>
+      <c r="E107" t="s">
+        <v>83</v>
+      </c>
+      <c r="H107" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A108" s="2">
+        <v>46227</v>
+      </c>
+      <c r="B108" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C108" t="s">
+        <v>105</v>
+      </c>
+      <c r="D108" t="s">
+        <v>41</v>
+      </c>
+      <c r="E108" t="s">
+        <v>83</v>
+      </c>
+      <c r="H108" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A109" s="2">
+        <v>46227</v>
+      </c>
+      <c r="B109" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C109" t="s">
+        <v>105</v>
+      </c>
+      <c r="D109" t="s">
+        <v>41</v>
+      </c>
+      <c r="E109" t="s">
+        <v>83</v>
+      </c>
+      <c r="H109" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A110" s="2">
+        <v>46227</v>
+      </c>
+      <c r="B110" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C110" t="s">
+        <v>105</v>
+      </c>
+      <c r="D110" t="s">
+        <v>41</v>
+      </c>
+      <c r="E110" t="s">
+        <v>83</v>
+      </c>
+      <c r="H110" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A111" s="2">
+        <v>46227</v>
+      </c>
+      <c r="B111" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C111" t="s">
+        <v>105</v>
+      </c>
+      <c r="D111" t="s">
+        <v>41</v>
+      </c>
+      <c r="E111" t="s">
+        <v>83</v>
+      </c>
+      <c r="H111" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A112" s="2">
+        <v>46227</v>
+      </c>
+      <c r="B112" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C112" t="s">
+        <v>105</v>
+      </c>
+      <c r="D112" t="s">
+        <v>41</v>
+      </c>
+      <c r="E112" t="s">
+        <v>52</v>
+      </c>
+      <c r="F112">
+        <v>54</v>
+      </c>
+      <c r="G112">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A113" s="2">
+        <v>46227</v>
+      </c>
+      <c r="B113" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C113" t="s">
+        <v>105</v>
+      </c>
+      <c r="D113" t="s">
+        <v>96</v>
+      </c>
+      <c r="E113" t="s">
+        <v>6</v>
+      </c>
+      <c r="F113">
+        <v>95</v>
+      </c>
+      <c r="G113">
+        <v>8900</v>
+      </c>
+      <c r="I113" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A114" s="2">
+        <v>46227</v>
+      </c>
+      <c r="B114" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C114" t="s">
+        <v>104</v>
+      </c>
+      <c r="D114" t="s">
+        <v>40</v>
+      </c>
+      <c r="E114" t="s">
+        <v>103</v>
+      </c>
+      <c r="F114">
+        <v>45</v>
+      </c>
+      <c r="G114">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A115" s="2">
+        <v>46227</v>
+      </c>
+      <c r="B115" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C115" t="s">
+        <v>105</v>
+      </c>
+      <c r="D115" t="s">
+        <v>96</v>
+      </c>
+      <c r="E115" t="s">
+        <v>68</v>
+      </c>
+      <c r="F115">
+        <v>94</v>
+      </c>
+      <c r="G115">
+        <v>8950</v>
+      </c>
+      <c r="I115" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A116" s="2">
+        <v>46227</v>
+      </c>
+      <c r="B116" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C116" t="s">
+        <v>104</v>
+      </c>
+      <c r="D116" t="s">
+        <v>40</v>
+      </c>
+      <c r="E116" t="s">
+        <v>103</v>
+      </c>
+      <c r="F116">
+        <v>45</v>
+      </c>
+      <c r="G116">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A117" s="2">
+        <v>46227</v>
+      </c>
+      <c r="B117" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C117" t="s">
+        <v>104</v>
+      </c>
+      <c r="D117" t="s">
+        <v>40</v>
+      </c>
+      <c r="E117" t="s">
+        <v>83</v>
+      </c>
+      <c r="F117">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A118" s="2">
+        <v>46227</v>
+      </c>
+      <c r="B118" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C118" t="s">
+        <v>104</v>
+      </c>
+      <c r="D118" t="s">
+        <v>40</v>
+      </c>
+      <c r="E118" t="s">
+        <v>83</v>
+      </c>
+      <c r="F118">
+        <v>35</v>
+      </c>
+      <c r="G118">
+        <v>360</v>
+      </c>
+      <c r="H118" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -2702,6 +3582,9 @@
       <c r="I2" s="6">
         <v>15.481199999999999</v>
       </c>
+      <c r="J2" s="12">
+        <v>2</v>
+      </c>
       <c r="K2">
         <v>14</v>
       </c>
@@ -2718,7 +3601,7 @@
         <v>49</v>
       </c>
       <c r="R2" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.35">
@@ -2749,7 +3632,7 @@
       <c r="I3" s="6">
         <v>15.481199999999999</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="12">
         <v>2</v>
       </c>
       <c r="K3">
@@ -2802,7 +3685,7 @@
       <c r="I4" s="6">
         <v>15.458</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="12">
         <v>2</v>
       </c>
       <c r="K4">
@@ -2855,7 +3738,7 @@
       <c r="I5" s="6">
         <v>15.3994</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="12">
         <v>2</v>
       </c>
       <c r="K5">
@@ -2908,7 +3791,7 @@
       <c r="I6" s="6">
         <v>15.481199999999999</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="12">
         <v>1</v>
       </c>
       <c r="K6">
@@ -2958,7 +3841,7 @@
       <c r="I7" s="6">
         <v>15.458</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="12">
         <v>1</v>
       </c>
       <c r="K7">
@@ -3008,7 +3891,7 @@
       <c r="I8" s="6">
         <v>15.7844</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="12">
         <v>2</v>
       </c>
       <c r="K8">
@@ -3064,7 +3947,7 @@
       <c r="I9" s="6">
         <v>15.738899999999999</v>
       </c>
-      <c r="J9">
+      <c r="J9" s="12">
         <v>1</v>
       </c>
       <c r="K9">
@@ -3117,7 +4000,7 @@
       <c r="I10" s="6">
         <v>15.6995</v>
       </c>
-      <c r="J10">
+      <c r="J10" s="12">
         <v>2</v>
       </c>
       <c r="K10">
@@ -3170,7 +4053,7 @@
       <c r="I11" s="6">
         <v>15.5815</v>
       </c>
-      <c r="J11">
+      <c r="J11" s="12">
         <v>1</v>
       </c>
       <c r="K11">
@@ -3223,7 +4106,7 @@
       <c r="I12" s="6">
         <v>15.7844</v>
       </c>
-      <c r="J12">
+      <c r="J12" s="12">
         <v>2</v>
       </c>
       <c r="K12">
@@ -3276,7 +4159,7 @@
       <c r="I13" s="6">
         <v>15.272</v>
       </c>
-      <c r="J13">
+      <c r="J13" s="12">
         <v>2</v>
       </c>
       <c r="K13" s="6">
@@ -3323,7 +4206,7 @@
       <c r="I14" s="6">
         <v>15.217700000000001</v>
       </c>
-      <c r="J14" s="6">
+      <c r="J14" s="12">
         <v>3</v>
       </c>
       <c r="K14" s="6">
@@ -3370,7 +4253,7 @@
       <c r="I15" s="6">
         <v>15.138999999999999</v>
       </c>
-      <c r="J15" s="6">
+      <c r="J15" s="12">
         <v>2</v>
       </c>
       <c r="K15" s="6">
@@ -3417,7 +4300,7 @@
       <c r="I16" s="6">
         <v>15.414999999999999</v>
       </c>
-      <c r="J16" s="6">
+      <c r="J16" s="12">
         <v>3</v>
       </c>
       <c r="K16" s="6">
@@ -3464,7 +4347,7 @@
       <c r="I17" s="6">
         <v>15.481199999999999</v>
       </c>
-      <c r="J17">
+      <c r="J17" s="12">
         <v>2</v>
       </c>
       <c r="K17">
@@ -3511,7 +4394,7 @@
       <c r="I18" s="6">
         <v>15.481199999999999</v>
       </c>
-      <c r="J18" s="6">
+      <c r="J18" s="12">
         <v>1</v>
       </c>
       <c r="K18">
@@ -3561,7 +4444,7 @@
       <c r="I19" s="6">
         <v>15.3994</v>
       </c>
-      <c r="J19" s="6">
+      <c r="J19" s="12">
         <v>2</v>
       </c>
       <c r="K19">
@@ -3611,7 +4494,7 @@
       <c r="I20" s="6">
         <v>15.481199999999999</v>
       </c>
-      <c r="J20" s="6">
+      <c r="J20" s="12">
         <v>2</v>
       </c>
       <c r="K20">
@@ -3661,7 +4544,7 @@
       <c r="I21" s="6">
         <v>15.481199999999999</v>
       </c>
-      <c r="J21" s="6">
+      <c r="J21" s="12">
         <v>2</v>
       </c>
       <c r="K21">
@@ -3711,7 +4594,7 @@
       <c r="I22" s="6">
         <v>15.481199999999999</v>
       </c>
-      <c r="J22" s="6">
+      <c r="J22" s="12">
         <v>2</v>
       </c>
       <c r="K22">
@@ -3761,7 +4644,7 @@
       <c r="I23" s="6">
         <v>15.1264</v>
       </c>
-      <c r="J23" s="6">
+      <c r="J23" s="12">
         <v>4</v>
       </c>
       <c r="K23" s="6">
@@ -3811,7 +4694,7 @@
       <c r="I24" s="6">
         <v>15.1318</v>
       </c>
-      <c r="J24" s="6">
+      <c r="J24" s="12">
         <v>4</v>
       </c>
       <c r="K24" s="6">
@@ -3867,7 +4750,7 @@
       <c r="I25" s="6">
         <v>15.3994</v>
       </c>
-      <c r="J25" s="6">
+      <c r="J25" s="12">
         <v>4</v>
       </c>
       <c r="K25" s="6">
@@ -3920,7 +4803,7 @@
       <c r="I26" s="6">
         <v>15.3994</v>
       </c>
-      <c r="J26" s="6">
+      <c r="J26" s="12">
         <v>4</v>
       </c>
       <c r="K26" s="6">
@@ -3976,7 +4859,7 @@
       <c r="I27" s="6">
         <v>15.7844</v>
       </c>
-      <c r="J27" s="6">
+      <c r="J27" s="12">
         <v>3</v>
       </c>
       <c r="K27">
@@ -4026,7 +4909,7 @@
       <c r="I28" s="6">
         <v>15.5144</v>
       </c>
-      <c r="J28" s="6">
+      <c r="J28" s="12">
         <v>4</v>
       </c>
       <c r="K28" s="6">
@@ -4076,7 +4959,7 @@
       <c r="I29" s="6">
         <v>15.481199999999999</v>
       </c>
-      <c r="J29" s="6">
+      <c r="J29" s="12">
         <v>3</v>
       </c>
       <c r="K29" s="6">
@@ -4105,96 +4988,439 @@
       </c>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="C30" s="4"/>
-      <c r="D30" s="3"/>
-      <c r="E30" s="3"/>
+      <c r="A30" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="B30" t="s">
+        <v>53</v>
+      </c>
+      <c r="C30" s="2">
+        <v>46187</v>
+      </c>
+      <c r="D30" s="3">
+        <v>0.46041666666666664</v>
+      </c>
+      <c r="E30" s="3">
+        <v>0.5444444444444444</v>
+      </c>
+      <c r="F30" s="6">
+        <v>67.531400000000005</v>
+      </c>
+      <c r="G30" s="6">
+        <v>15.6182</v>
+      </c>
+      <c r="H30" s="6">
+        <v>67.531400000000005</v>
+      </c>
+      <c r="I30" s="6">
+        <v>15.6182</v>
+      </c>
+      <c r="J30" s="12">
+        <v>1</v>
+      </c>
+      <c r="K30" s="6">
+        <v>55</v>
+      </c>
+      <c r="L30" s="6">
+        <v>75</v>
+      </c>
+      <c r="O30" t="s">
+        <v>37</v>
+      </c>
+      <c r="P30" s="6">
+        <v>300</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>38</v>
+      </c>
+      <c r="R30" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="C31" s="4"/>
-      <c r="D31" s="3"/>
-      <c r="E31" s="3"/>
+      <c r="A31" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="B31" t="s">
+        <v>53</v>
+      </c>
+      <c r="C31" s="2">
+        <v>46200</v>
+      </c>
+      <c r="D31" s="3">
+        <v>0.60347222222222219</v>
+      </c>
+      <c r="E31" s="3">
+        <v>0.65555555555555556</v>
+      </c>
+      <c r="F31" s="6">
+        <v>67.531400000000005</v>
+      </c>
+      <c r="G31" s="6">
+        <v>15.6182</v>
+      </c>
+      <c r="H31" s="6">
+        <v>67.531400000000005</v>
+      </c>
+      <c r="I31" s="6">
+        <v>15.6182</v>
+      </c>
+      <c r="J31" s="12">
+        <v>1</v>
+      </c>
+      <c r="K31" s="6">
+        <v>30</v>
+      </c>
+      <c r="L31" s="6">
+        <v>60</v>
+      </c>
+      <c r="M31" s="6">
+        <v>13</v>
+      </c>
+      <c r="N31" s="6">
+        <v>26.7</v>
+      </c>
+      <c r="O31" t="s">
+        <v>55</v>
+      </c>
+      <c r="P31" s="6">
+        <v>140</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>38</v>
+      </c>
+      <c r="R31" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="C32" s="4"/>
-      <c r="D32" s="3"/>
-      <c r="E32" s="3"/>
-    </row>
-    <row r="33" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C33" s="4"/>
-      <c r="D33" s="3"/>
-      <c r="E33" s="3"/>
-    </row>
-    <row r="34" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C34" s="4"/>
-      <c r="D34" s="3"/>
-      <c r="E34" s="3"/>
-    </row>
-    <row r="35" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C35" s="4"/>
-      <c r="D35" s="3"/>
-      <c r="E35" s="3"/>
-    </row>
-    <row r="36" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C36" s="4"/>
-      <c r="D36" s="3"/>
-      <c r="E36" s="3"/>
-    </row>
-    <row r="37" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="A32" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B32" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="2">
+        <v>46210</v>
+      </c>
+      <c r="D32" s="3">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="E32" s="3">
+        <v>0.72569444444444442</v>
+      </c>
+      <c r="F32" s="6">
+        <v>67.503900000000002</v>
+      </c>
+      <c r="G32" s="6">
+        <v>15.3994</v>
+      </c>
+      <c r="H32" s="6">
+        <v>67.503900000000002</v>
+      </c>
+      <c r="I32" s="6">
+        <v>15.3994</v>
+      </c>
+      <c r="J32" s="12">
+        <v>1</v>
+      </c>
+      <c r="K32">
+        <v>21</v>
+      </c>
+      <c r="L32">
+        <v>35</v>
+      </c>
+      <c r="O32" t="s">
+        <v>36</v>
+      </c>
+      <c r="P32" s="6">
+        <v>233</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>38</v>
+      </c>
+      <c r="R32" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A33" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B33" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="2">
+        <v>46223</v>
+      </c>
+      <c r="D33" s="3">
+        <v>0.60763888888888884</v>
+      </c>
+      <c r="E33" s="3">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="F33" s="6">
+        <v>67.516000000000005</v>
+      </c>
+      <c r="G33" s="6">
+        <v>15.481199999999999</v>
+      </c>
+      <c r="H33" s="6">
+        <v>67.516000000000005</v>
+      </c>
+      <c r="I33" s="6">
+        <v>15.481199999999999</v>
+      </c>
+      <c r="J33" s="12">
+        <v>3</v>
+      </c>
+      <c r="K33" s="6">
+        <v>15</v>
+      </c>
+      <c r="L33" s="6">
+        <v>55</v>
+      </c>
+      <c r="M33" s="6">
+        <v>13.2</v>
+      </c>
+      <c r="N33" s="6">
+        <v>26</v>
+      </c>
+      <c r="O33" t="s">
+        <v>36</v>
+      </c>
+      <c r="P33" s="6">
+        <v>145</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>38</v>
+      </c>
+      <c r="R33" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A34" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B34" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="2">
+        <v>46223</v>
+      </c>
+      <c r="D34" s="3">
+        <v>0.64930555555555558</v>
+      </c>
+      <c r="E34" s="3">
+        <v>0.67013888888888884</v>
+      </c>
+      <c r="F34" s="6">
+        <v>67.503900000000002</v>
+      </c>
+      <c r="G34" s="6">
+        <v>15.3994</v>
+      </c>
+      <c r="H34" s="6">
+        <v>67.503900000000002</v>
+      </c>
+      <c r="I34" s="6">
+        <v>15.3994</v>
+      </c>
+      <c r="J34" s="12">
+        <v>2</v>
+      </c>
+      <c r="K34" s="6">
+        <v>10</v>
+      </c>
+      <c r="L34" s="6">
+        <v>30</v>
+      </c>
+      <c r="M34" s="6">
+        <v>13.2</v>
+      </c>
+      <c r="N34" s="6">
+        <v>26</v>
+      </c>
+      <c r="O34" t="s">
+        <v>36</v>
+      </c>
+      <c r="P34" s="6">
+        <v>205</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>38</v>
+      </c>
+      <c r="R34" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A35" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="B35" t="s">
+        <v>75</v>
+      </c>
+      <c r="C35" s="2">
+        <v>46223</v>
+      </c>
+      <c r="D35" s="3">
+        <v>0.68472222222222223</v>
+      </c>
+      <c r="E35" s="3">
+        <v>0.70486111111111116</v>
+      </c>
+      <c r="F35" s="6">
+        <v>67.299700000000001</v>
+      </c>
+      <c r="G35" s="6">
+        <v>15.166399999999999</v>
+      </c>
+      <c r="H35" s="6">
+        <v>67.299700000000001</v>
+      </c>
+      <c r="I35" s="6">
+        <v>15.166399999999999</v>
+      </c>
+      <c r="J35" s="12">
+        <v>3</v>
+      </c>
+      <c r="K35" s="6">
+        <v>10</v>
+      </c>
+      <c r="L35" s="6">
+        <v>20</v>
+      </c>
+      <c r="M35" s="6">
+        <v>13.3</v>
+      </c>
+      <c r="N35" s="6">
+        <v>27</v>
+      </c>
+      <c r="O35" t="s">
+        <v>36</v>
+      </c>
+      <c r="P35" s="6">
+        <v>225</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>38</v>
+      </c>
+      <c r="R35" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A36" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="B36" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="2">
+        <v>46227</v>
+      </c>
+      <c r="D36" s="3">
+        <v>0.62708333333333333</v>
+      </c>
+      <c r="E36" s="3">
+        <v>0.75069444444444444</v>
+      </c>
+      <c r="F36" s="6">
+        <v>67.503900000000002</v>
+      </c>
+      <c r="G36" s="6">
+        <v>15.3994</v>
+      </c>
+      <c r="H36" s="6">
+        <v>67.503900000000002</v>
+      </c>
+      <c r="I36" s="6">
+        <v>15.3994</v>
+      </c>
+      <c r="J36" s="12">
+        <v>2</v>
+      </c>
+      <c r="K36">
+        <v>30</v>
+      </c>
+      <c r="L36">
+        <v>45</v>
+      </c>
+      <c r="O36" t="s">
+        <v>36</v>
+      </c>
+      <c r="P36" s="6">
+        <v>150</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>38</v>
+      </c>
+      <c r="R36" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A37" s="9"/>
       <c r="C37" s="4"/>
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
     </row>
-    <row r="38" spans="3:5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A38" s="9"/>
       <c r="C38" s="4"/>
       <c r="D38" s="3"/>
       <c r="E38" s="3"/>
     </row>
-    <row r="39" spans="3:5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A39" s="9"/>
       <c r="C39" s="4"/>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
     </row>
-    <row r="40" spans="3:5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A40" s="9"/>
       <c r="C40" s="4"/>
       <c r="D40" s="3"/>
       <c r="E40" s="3"/>
     </row>
-    <row r="41" spans="3:5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.35">
       <c r="C41" s="4"/>
       <c r="D41" s="3"/>
       <c r="E41" s="3"/>
     </row>
-    <row r="42" spans="3:5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.35">
       <c r="C42" s="4"/>
       <c r="D42" s="3"/>
       <c r="E42" s="3"/>
     </row>
-    <row r="43" spans="3:5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.35">
       <c r="C43" s="4"/>
       <c r="D43" s="3"/>
       <c r="E43" s="3"/>
     </row>
-    <row r="44" spans="3:5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:18" x14ac:dyDescent="0.35">
       <c r="C44" s="4"/>
       <c r="D44" s="3"/>
       <c r="E44" s="3"/>
     </row>
-    <row r="45" spans="3:5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:18" x14ac:dyDescent="0.35">
       <c r="C45" s="4"/>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
     </row>
-    <row r="46" spans="3:5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.35">
       <c r="C46" s="4"/>
       <c r="D46" s="3"/>
       <c r="E46" s="3"/>
     </row>
-    <row r="47" spans="3:5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:18" x14ac:dyDescent="0.35">
       <c r="C47" s="4"/>
       <c r="D47" s="3"/>
       <c r="E47" s="3"/>
     </row>
-    <row r="48" spans="3:5" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:18" x14ac:dyDescent="0.35">
       <c r="C48" s="4"/>
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>

--- a/Survey_data_real.xlsx
+++ b/Survey_data_real.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop (1)\Other\ShinyAPPnorway\ACCESS-FjordAPP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE680AB4-F6EA-4EE6-8E68-F2B8A9F493FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F496B0B-A355-47C3-814C-0C56738B4DC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="stratum_info" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">catchdata!$A$1:$H$997</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">catchdata!$A$1:$J$118</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">station_info!$A$1:$S$216</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="717" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="830" uniqueCount="123">
   <si>
     <t>Date</t>
   </si>
@@ -367,6 +367,45 @@
   </si>
   <si>
     <t>small crab</t>
+  </si>
+  <si>
+    <t>Fiskebrigga corner</t>
+  </si>
+  <si>
+    <t>Goal</t>
+  </si>
+  <si>
+    <t>Skarvstua</t>
+  </si>
+  <si>
+    <t>Sjunkvika</t>
+  </si>
+  <si>
+    <t>Seatrout</t>
+  </si>
+  <si>
+    <t>Rørstad port</t>
+  </si>
+  <si>
+    <t>Aniello</t>
+  </si>
+  <si>
+    <t>3 shells</t>
+  </si>
+  <si>
+    <t>NPTF</t>
+  </si>
+  <si>
+    <t>NP</t>
+  </si>
+  <si>
+    <t>lost 4 halibut</t>
+  </si>
+  <si>
+    <t>lost 2 halibut</t>
+  </si>
+  <si>
+    <t>lost 2/3 halibut</t>
   </si>
 </sst>
 </file>
@@ -428,7 +467,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -440,10 +479,7 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -748,7 +784,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I118"/>
+  <dimension ref="A1:J132"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="25.7265625" style="2" customWidth="1"/>
@@ -756,10 +792,10 @@
     <col min="3" max="3" width="21" customWidth="1"/>
     <col min="4" max="4" width="13.7265625" customWidth="1"/>
     <col min="5" max="5" width="19.1796875" customWidth="1"/>
-    <col min="9" max="9" width="17.6328125" customWidth="1"/>
+    <col min="10" max="10" width="17.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" s="1" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -782,13 +818,16 @@
         <v>4</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
         <v>45997</v>
       </c>
@@ -811,7 +850,7 @@
         <v>8000</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <v>45997</v>
       </c>
@@ -833,11 +872,11 @@
       <c r="G3">
         <v>1046</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="I3" s="8" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>45997</v>
       </c>
@@ -859,11 +898,11 @@
       <c r="G4">
         <v>880</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>46062</v>
       </c>
@@ -877,7 +916,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>46062</v>
       </c>
@@ -900,7 +939,7 @@
         <v>2090</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <v>46062</v>
       </c>
@@ -923,7 +962,7 @@
         <v>2070</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>46062</v>
       </c>
@@ -945,11 +984,11 @@
       <c r="G8">
         <v>200</v>
       </c>
-      <c r="H8" t="s">
+      <c r="I8" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
         <v>46062</v>
       </c>
@@ -971,11 +1010,11 @@
       <c r="G9">
         <v>500</v>
       </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <v>46062</v>
       </c>
@@ -998,7 +1037,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
         <v>46062</v>
       </c>
@@ -1020,11 +1059,11 @@
       <c r="G11">
         <v>580</v>
       </c>
-      <c r="H11" t="s">
+      <c r="I11" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>46074</v>
       </c>
@@ -1047,7 +1086,7 @@
         <v>11120</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <v>46074</v>
       </c>
@@ -1069,11 +1108,11 @@
       <c r="G13">
         <v>3200</v>
       </c>
-      <c r="H13" t="s">
+      <c r="I13" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <v>46074</v>
       </c>
@@ -1095,11 +1134,11 @@
       <c r="G14">
         <v>2300</v>
       </c>
-      <c r="H14" t="s">
+      <c r="I14" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
         <v>46074</v>
       </c>
@@ -1121,11 +1160,11 @@
       <c r="G15">
         <v>1000</v>
       </c>
-      <c r="H15" t="s">
+      <c r="I15" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <v>46082</v>
       </c>
@@ -1148,7 +1187,7 @@
         <v>1140</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
         <v>46082</v>
       </c>
@@ -1170,11 +1209,11 @@
       <c r="G17">
         <v>1300</v>
       </c>
-      <c r="H17" t="s">
+      <c r="I17" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <v>46082</v>
       </c>
@@ -1196,11 +1235,11 @@
       <c r="G18">
         <v>5000</v>
       </c>
-      <c r="H18" t="s">
+      <c r="I18" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
         <v>46082</v>
       </c>
@@ -1222,11 +1261,11 @@
       <c r="G19">
         <v>3300</v>
       </c>
-      <c r="I19" t="s">
+      <c r="J19" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
         <v>46082</v>
       </c>
@@ -1248,11 +1287,11 @@
       <c r="G20">
         <v>3100</v>
       </c>
-      <c r="H20" t="s">
+      <c r="I20" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
         <v>46082</v>
       </c>
@@ -1274,11 +1313,11 @@
       <c r="G21">
         <v>2200</v>
       </c>
-      <c r="I21" t="s">
+      <c r="J21" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
         <v>46082</v>
       </c>
@@ -1300,11 +1339,11 @@
       <c r="G22">
         <v>1250</v>
       </c>
-      <c r="I22" t="s">
+      <c r="J22" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
         <v>46082</v>
       </c>
@@ -1327,7 +1366,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
         <v>46082</v>
       </c>
@@ -1349,11 +1388,11 @@
       <c r="G24">
         <v>1430</v>
       </c>
-      <c r="I24" t="s">
+      <c r="J24" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
         <v>46082</v>
       </c>
@@ -1375,11 +1414,11 @@
       <c r="G25">
         <v>2600</v>
       </c>
-      <c r="H25" t="s">
+      <c r="I25" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
         <v>46082</v>
       </c>
@@ -1402,7 +1441,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27" s="2">
         <v>46082</v>
       </c>
@@ -1416,7 +1455,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
         <v>46095</v>
       </c>
@@ -1439,7 +1478,7 @@
         <v>3470</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29" s="2">
         <v>46095</v>
       </c>
@@ -1461,11 +1500,11 @@
       <c r="G29">
         <v>3010</v>
       </c>
-      <c r="H29" t="s">
+      <c r="I29" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30" s="2">
         <v>46095</v>
       </c>
@@ -1488,7 +1527,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31" s="2">
         <v>46095</v>
       </c>
@@ -1510,11 +1549,11 @@
       <c r="G31">
         <v>17155</v>
       </c>
-      <c r="H31" t="s">
+      <c r="I31" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32" s="2">
         <v>46095</v>
       </c>
@@ -1536,7 +1575,7 @@
       <c r="G32">
         <v>3695</v>
       </c>
-      <c r="I32" t="s">
+      <c r="J32" t="s">
         <v>70</v>
       </c>
     </row>
@@ -1899,7 +1938,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A49" s="2">
         <v>46116</v>
       </c>
@@ -1922,7 +1961,7 @@
         <v>1375</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A50" s="2">
         <v>46116</v>
       </c>
@@ -1945,7 +1984,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A51" s="2">
         <v>46116</v>
       </c>
@@ -1968,7 +2007,7 @@
         <v>2570</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A52" s="2">
         <v>46116</v>
       </c>
@@ -1991,7 +2030,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A53" s="2">
         <v>46116</v>
       </c>
@@ -2014,7 +2053,7 @@
         <v>11680</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A54" s="2">
         <v>46142</v>
       </c>
@@ -2037,7 +2076,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A55" s="2">
         <v>46150</v>
       </c>
@@ -2060,7 +2099,7 @@
         <v>2300</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A56" s="2">
         <v>46150</v>
       </c>
@@ -2083,7 +2122,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A57" s="2">
         <v>46150</v>
       </c>
@@ -2105,11 +2144,11 @@
       <c r="G57">
         <v>660</v>
       </c>
-      <c r="H57" t="s">
+      <c r="I57" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A58" s="2">
         <v>46158</v>
       </c>
@@ -2123,7 +2162,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A59" s="2">
         <v>46159</v>
       </c>
@@ -2146,7 +2185,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A60" s="2">
         <v>46159</v>
       </c>
@@ -2169,7 +2208,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A61" s="2">
         <v>46162</v>
       </c>
@@ -2192,7 +2231,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A62" s="2">
         <v>46162</v>
       </c>
@@ -2215,7 +2254,7 @@
         <v>823</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A63" s="2">
         <v>46162</v>
       </c>
@@ -2238,7 +2277,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A64" s="2">
         <v>46162</v>
       </c>
@@ -2260,11 +2299,11 @@
       <c r="G64">
         <v>867</v>
       </c>
-      <c r="H64" t="s">
+      <c r="I64" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A65" s="2">
         <v>46172</v>
       </c>
@@ -2287,7 +2326,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A66" s="2">
         <v>46172</v>
       </c>
@@ -2307,7 +2346,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A67" s="2">
         <v>46172</v>
       </c>
@@ -2327,7 +2366,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A68" s="2">
         <v>46172</v>
       </c>
@@ -2347,7 +2386,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A69" s="2">
         <v>46172</v>
       </c>
@@ -2367,7 +2406,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A70" s="2">
         <v>46172</v>
       </c>
@@ -2386,11 +2425,11 @@
       <c r="F70">
         <v>45</v>
       </c>
-      <c r="H70" t="s">
+      <c r="I70" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A71" s="2">
         <v>46172</v>
       </c>
@@ -2409,11 +2448,11 @@
       <c r="F71">
         <v>43</v>
       </c>
-      <c r="H71" t="s">
+      <c r="I71" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A72" s="2">
         <v>46172</v>
       </c>
@@ -2433,7 +2472,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A73" s="2">
         <v>46172</v>
       </c>
@@ -2455,11 +2494,11 @@
       <c r="G73">
         <v>3400</v>
       </c>
-      <c r="H73" t="s">
+      <c r="I73" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A74" s="2">
         <v>46172</v>
       </c>
@@ -2479,7 +2518,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A75" s="2">
         <v>46172</v>
       </c>
@@ -2502,7 +2541,7 @@
         <v>4600</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A76" s="2">
         <v>46172</v>
       </c>
@@ -2525,7 +2564,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A77" s="2">
         <v>46173</v>
       </c>
@@ -2545,7 +2584,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A78" s="2">
         <v>46173</v>
       </c>
@@ -2568,7 +2607,7 @@
         <v>13000</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A79" s="2">
         <v>46173</v>
       </c>
@@ -2587,11 +2626,11 @@
       <c r="F79">
         <v>35</v>
       </c>
-      <c r="H79" t="s">
+      <c r="I79" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A80" s="2">
         <v>46173</v>
       </c>
@@ -2614,11 +2653,11 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A81" s="2">
         <v>46173</v>
       </c>
-      <c r="B81" s="10" t="s">
+      <c r="B81" s="9" t="s">
         <v>42</v>
       </c>
       <c r="C81" t="s">
@@ -2637,11 +2676,11 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A82" s="2">
         <v>46187</v>
       </c>
-      <c r="B82" s="11" t="s">
+      <c r="B82" s="9" t="s">
         <v>97</v>
       </c>
       <c r="C82" t="s">
@@ -2660,11 +2699,11 @@
         <v>3150</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A83" s="2">
         <v>46187</v>
       </c>
-      <c r="B83" s="11" t="s">
+      <c r="B83" s="9" t="s">
         <v>97</v>
       </c>
       <c r="C83" t="s">
@@ -2683,11 +2722,11 @@
         <v>4400</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A84" s="2">
         <v>46187</v>
       </c>
-      <c r="B84" s="11" t="s">
+      <c r="B84" s="9" t="s">
         <v>97</v>
       </c>
       <c r="C84" t="s">
@@ -2703,11 +2742,11 @@
         <v>55</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A85" s="2">
         <v>46200</v>
       </c>
-      <c r="B85" s="11" t="s">
+      <c r="B85" s="9" t="s">
         <v>97</v>
       </c>
       <c r="C85" t="s">
@@ -2726,11 +2765,11 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A86" s="2">
         <v>46200</v>
       </c>
-      <c r="B86" s="11" t="s">
+      <c r="B86" s="9" t="s">
         <v>97</v>
       </c>
       <c r="C86" t="s">
@@ -2749,11 +2788,11 @@
         <v>1650</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A87" s="2">
         <v>46200</v>
       </c>
-      <c r="B87" s="11" t="s">
+      <c r="B87" s="9" t="s">
         <v>97</v>
       </c>
       <c r="C87" t="s">
@@ -2772,11 +2811,11 @@
         <v>1350</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A88" s="2">
         <v>46200</v>
       </c>
-      <c r="B88" s="11" t="s">
+      <c r="B88" s="9" t="s">
         <v>97</v>
       </c>
       <c r="C88" t="s">
@@ -2794,15 +2833,15 @@
       <c r="G88">
         <v>465</v>
       </c>
-      <c r="H88" t="s">
+      <c r="I88" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A89" s="2">
         <v>46210</v>
       </c>
-      <c r="B89" s="10" t="s">
+      <c r="B89" s="9" t="s">
         <v>44</v>
       </c>
       <c r="C89" t="s">
@@ -2821,7 +2860,7 @@
         <v>9000</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A90" s="2">
         <v>46210</v>
       </c>
@@ -2844,7 +2883,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A91" s="2">
         <v>46210</v>
       </c>
@@ -2861,7 +2900,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A92" s="2">
         <v>46223</v>
       </c>
@@ -2883,11 +2922,11 @@
       <c r="G92">
         <v>4400</v>
       </c>
-      <c r="I92" t="s">
+      <c r="J92" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A93" s="2">
         <v>46223</v>
       </c>
@@ -2909,11 +2948,11 @@
       <c r="G93">
         <v>700</v>
       </c>
-      <c r="H93" t="s">
+      <c r="I93" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A94" s="2">
         <v>46223</v>
       </c>
@@ -2930,7 +2969,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A95" s="2">
         <v>46223</v>
       </c>
@@ -2947,11 +2986,11 @@
         <v>83</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A96" s="2">
         <v>46223</v>
       </c>
-      <c r="B96" s="9" t="s">
+      <c r="B96" t="s">
         <v>98</v>
       </c>
       <c r="C96" t="s">
@@ -2970,11 +3009,11 @@
         <v>1120</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A97" s="2">
         <v>46223</v>
       </c>
-      <c r="B97" s="9" t="s">
+      <c r="B97" t="s">
         <v>98</v>
       </c>
       <c r="C97" t="s">
@@ -2992,15 +3031,15 @@
       <c r="G97">
         <v>5800</v>
       </c>
-      <c r="I97" t="s">
+      <c r="J97" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A98" s="2">
         <v>46223</v>
       </c>
-      <c r="B98" s="9" t="s">
+      <c r="B98" t="s">
         <v>98</v>
       </c>
       <c r="C98" t="s">
@@ -3018,15 +3057,15 @@
       <c r="G98">
         <v>3900</v>
       </c>
-      <c r="H98" t="s">
+      <c r="I98" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A99" s="2">
         <v>46223</v>
       </c>
-      <c r="B99" s="9" t="s">
+      <c r="B99" t="s">
         <v>98</v>
       </c>
       <c r="C99" t="s">
@@ -3044,15 +3083,15 @@
       <c r="G99">
         <v>1060</v>
       </c>
-      <c r="I99" t="s">
+      <c r="J99" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A100" s="2">
         <v>46227</v>
       </c>
-      <c r="B100" s="9" t="s">
+      <c r="B100" t="s">
         <v>44</v>
       </c>
       <c r="C100" t="s">
@@ -3071,11 +3110,11 @@
         <v>350</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A101" s="2">
         <v>46227</v>
       </c>
-      <c r="B101" s="9" t="s">
+      <c r="B101" t="s">
         <v>44</v>
       </c>
       <c r="C101" t="s">
@@ -3094,11 +3133,11 @@
         <v>300</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A102" s="2">
         <v>46227</v>
       </c>
-      <c r="B102" s="9" t="s">
+      <c r="B102" t="s">
         <v>44</v>
       </c>
       <c r="C102" t="s">
@@ -3114,11 +3153,11 @@
         <v>34</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A103" s="2">
         <v>46227</v>
       </c>
-      <c r="B103" s="9" t="s">
+      <c r="B103" t="s">
         <v>44</v>
       </c>
       <c r="C103" t="s">
@@ -3134,11 +3173,11 @@
         <v>35</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A104" s="2">
         <v>46227</v>
       </c>
-      <c r="B104" s="9" t="s">
+      <c r="B104" t="s">
         <v>44</v>
       </c>
       <c r="C104" t="s">
@@ -3157,11 +3196,11 @@
         <v>410</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A105" s="2">
         <v>46227</v>
       </c>
-      <c r="B105" s="9" t="s">
+      <c r="B105" t="s">
         <v>44</v>
       </c>
       <c r="C105" t="s">
@@ -3180,11 +3219,11 @@
         <v>375</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A106" s="2">
         <v>46227</v>
       </c>
-      <c r="B106" s="9" t="s">
+      <c r="B106" t="s">
         <v>44</v>
       </c>
       <c r="C106" t="s">
@@ -3196,15 +3235,15 @@
       <c r="E106" t="s">
         <v>83</v>
       </c>
-      <c r="H106" t="s">
+      <c r="I106" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A107" s="2">
         <v>46227</v>
       </c>
-      <c r="B107" s="9" t="s">
+      <c r="B107" t="s">
         <v>44</v>
       </c>
       <c r="C107" t="s">
@@ -3216,15 +3255,15 @@
       <c r="E107" t="s">
         <v>83</v>
       </c>
-      <c r="H107" t="s">
+      <c r="I107" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A108" s="2">
         <v>46227</v>
       </c>
-      <c r="B108" s="9" t="s">
+      <c r="B108" t="s">
         <v>44</v>
       </c>
       <c r="C108" t="s">
@@ -3236,15 +3275,15 @@
       <c r="E108" t="s">
         <v>83</v>
       </c>
-      <c r="H108" t="s">
+      <c r="I108" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A109" s="2">
         <v>46227</v>
       </c>
-      <c r="B109" s="9" t="s">
+      <c r="B109" t="s">
         <v>44</v>
       </c>
       <c r="C109" t="s">
@@ -3256,15 +3295,15 @@
       <c r="E109" t="s">
         <v>83</v>
       </c>
-      <c r="H109" t="s">
+      <c r="I109" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A110" s="2">
         <v>46227</v>
       </c>
-      <c r="B110" s="9" t="s">
+      <c r="B110" t="s">
         <v>44</v>
       </c>
       <c r="C110" t="s">
@@ -3276,15 +3315,15 @@
       <c r="E110" t="s">
         <v>83</v>
       </c>
-      <c r="H110" t="s">
+      <c r="I110" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A111" s="2">
         <v>46227</v>
       </c>
-      <c r="B111" s="9" t="s">
+      <c r="B111" t="s">
         <v>44</v>
       </c>
       <c r="C111" t="s">
@@ -3296,15 +3335,15 @@
       <c r="E111" t="s">
         <v>83</v>
       </c>
-      <c r="H111" t="s">
+      <c r="I111" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A112" s="2">
         <v>46227</v>
       </c>
-      <c r="B112" s="9" t="s">
+      <c r="B112" t="s">
         <v>44</v>
       </c>
       <c r="C112" t="s">
@@ -3323,11 +3362,11 @@
         <v>750</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A113" s="2">
         <v>46227</v>
       </c>
-      <c r="B113" s="9" t="s">
+      <c r="B113" t="s">
         <v>44</v>
       </c>
       <c r="C113" t="s">
@@ -3345,15 +3384,15 @@
       <c r="G113">
         <v>8900</v>
       </c>
-      <c r="I113" t="s">
+      <c r="J113" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A114" s="2">
         <v>46227</v>
       </c>
-      <c r="B114" s="9" t="s">
+      <c r="B114" t="s">
         <v>44</v>
       </c>
       <c r="C114" t="s">
@@ -3372,11 +3411,11 @@
         <v>650</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A115" s="2">
         <v>46227</v>
       </c>
-      <c r="B115" s="9" t="s">
+      <c r="B115" t="s">
         <v>44</v>
       </c>
       <c r="C115" t="s">
@@ -3394,15 +3433,15 @@
       <c r="G115">
         <v>8950</v>
       </c>
-      <c r="I115" t="s">
+      <c r="J115" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A116" s="2">
         <v>46227</v>
       </c>
-      <c r="B116" s="9" t="s">
+      <c r="B116" t="s">
         <v>44</v>
       </c>
       <c r="C116" t="s">
@@ -3421,11 +3460,11 @@
         <v>650</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A117" s="2">
         <v>46227</v>
       </c>
-      <c r="B117" s="9" t="s">
+      <c r="B117" t="s">
         <v>44</v>
       </c>
       <c r="C117" t="s">
@@ -3441,11 +3480,11 @@
         <v>50</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A118" s="2">
         <v>46227</v>
       </c>
-      <c r="B118" s="9" t="s">
+      <c r="B118" t="s">
         <v>44</v>
       </c>
       <c r="C118" t="s">
@@ -3463,8 +3502,348 @@
       <c r="G118">
         <v>360</v>
       </c>
-      <c r="H118" t="s">
+      <c r="I118" t="s">
         <v>8</v>
+      </c>
+    </row>
+    <row r="119" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A119" s="2">
+        <v>46243</v>
+      </c>
+      <c r="B119" t="s">
+        <v>110</v>
+      </c>
+      <c r="C119" t="s">
+        <v>85</v>
+      </c>
+      <c r="D119" t="s">
+        <v>41</v>
+      </c>
+      <c r="E119" t="s">
+        <v>83</v>
+      </c>
+      <c r="F119">
+        <v>26</v>
+      </c>
+      <c r="G119">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="120" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A120" s="2">
+        <v>46243</v>
+      </c>
+      <c r="B120" t="s">
+        <v>110</v>
+      </c>
+      <c r="C120" t="s">
+        <v>116</v>
+      </c>
+      <c r="D120" t="s">
+        <v>41</v>
+      </c>
+      <c r="E120" t="s">
+        <v>79</v>
+      </c>
+      <c r="F120">
+        <v>71</v>
+      </c>
+      <c r="G120">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="121" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A121" s="2">
+        <v>46243</v>
+      </c>
+      <c r="B121" t="s">
+        <v>54</v>
+      </c>
+      <c r="C121" t="s">
+        <v>86</v>
+      </c>
+      <c r="D121" t="s">
+        <v>41</v>
+      </c>
+      <c r="E121" t="s">
+        <v>83</v>
+      </c>
+      <c r="F121">
+        <v>37</v>
+      </c>
+      <c r="G121">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="122" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A122" s="2">
+        <v>46246</v>
+      </c>
+      <c r="B122" t="s">
+        <v>112</v>
+      </c>
+      <c r="C122" t="s">
+        <v>86</v>
+      </c>
+      <c r="D122" t="s">
+        <v>41</v>
+      </c>
+      <c r="E122" t="s">
+        <v>52</v>
+      </c>
+      <c r="F122">
+        <v>58</v>
+      </c>
+      <c r="G122">
+        <v>830</v>
+      </c>
+      <c r="H122" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="123" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A123" s="2">
+        <v>46246</v>
+      </c>
+      <c r="B123" t="s">
+        <v>112</v>
+      </c>
+      <c r="C123" t="s">
+        <v>116</v>
+      </c>
+      <c r="D123" t="s">
+        <v>41</v>
+      </c>
+      <c r="E123" t="s">
+        <v>79</v>
+      </c>
+      <c r="F123">
+        <v>62</v>
+      </c>
+      <c r="G123">
+        <v>1750</v>
+      </c>
+      <c r="H123" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="124" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A124" s="2">
+        <v>46246</v>
+      </c>
+      <c r="B124" t="s">
+        <v>113</v>
+      </c>
+      <c r="C124" t="s">
+        <v>116</v>
+      </c>
+      <c r="D124" t="s">
+        <v>41</v>
+      </c>
+      <c r="E124" t="s">
+        <v>83</v>
+      </c>
+      <c r="F124">
+        <v>26</v>
+      </c>
+      <c r="G124">
+        <v>175</v>
+      </c>
+      <c r="H124" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="125" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A125" s="2">
+        <v>46246</v>
+      </c>
+      <c r="B125" t="s">
+        <v>115</v>
+      </c>
+      <c r="C125" t="s">
+        <v>116</v>
+      </c>
+      <c r="D125" t="s">
+        <v>41</v>
+      </c>
+      <c r="E125" t="s">
+        <v>6</v>
+      </c>
+      <c r="F125">
+        <v>60</v>
+      </c>
+      <c r="G125">
+        <v>2000</v>
+      </c>
+      <c r="I125" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="126" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A126" s="2">
+        <v>46247</v>
+      </c>
+      <c r="B126" t="s">
+        <v>44</v>
+      </c>
+      <c r="C126" t="s">
+        <v>86</v>
+      </c>
+      <c r="D126" t="s">
+        <v>41</v>
+      </c>
+      <c r="E126" t="s">
+        <v>6</v>
+      </c>
+      <c r="F126">
+        <v>73</v>
+      </c>
+      <c r="G126">
+        <v>4080</v>
+      </c>
+      <c r="J126" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="127" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A127" s="2">
+        <v>46247</v>
+      </c>
+      <c r="B127" t="s">
+        <v>42</v>
+      </c>
+      <c r="C127" t="s">
+        <v>86</v>
+      </c>
+      <c r="D127" t="s">
+        <v>40</v>
+      </c>
+      <c r="E127" t="s">
+        <v>103</v>
+      </c>
+      <c r="F127">
+        <v>37</v>
+      </c>
+      <c r="G127">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="128" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A128" s="2">
+        <v>46247</v>
+      </c>
+      <c r="B128" t="s">
+        <v>42</v>
+      </c>
+      <c r="C128" t="s">
+        <v>86</v>
+      </c>
+      <c r="D128" t="s">
+        <v>40</v>
+      </c>
+      <c r="E128" t="s">
+        <v>103</v>
+      </c>
+      <c r="F128">
+        <v>38</v>
+      </c>
+      <c r="G128">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A129" s="2">
+        <v>46248</v>
+      </c>
+      <c r="B129" t="s">
+        <v>44</v>
+      </c>
+      <c r="C129" t="s">
+        <v>86</v>
+      </c>
+      <c r="D129" t="s">
+        <v>96</v>
+      </c>
+      <c r="E129" t="s">
+        <v>6</v>
+      </c>
+      <c r="F129">
+        <v>76</v>
+      </c>
+      <c r="G129">
+        <v>4200</v>
+      </c>
+      <c r="J129" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A130" s="2">
+        <v>46248</v>
+      </c>
+      <c r="B130" t="s">
+        <v>44</v>
+      </c>
+      <c r="C130" t="s">
+        <v>116</v>
+      </c>
+      <c r="D130" t="s">
+        <v>40</v>
+      </c>
+      <c r="E130" t="s">
+        <v>83</v>
+      </c>
+      <c r="F130">
+        <v>46</v>
+      </c>
+      <c r="G130">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A131" s="2">
+        <v>46248</v>
+      </c>
+      <c r="B131" t="s">
+        <v>44</v>
+      </c>
+      <c r="C131" t="s">
+        <v>116</v>
+      </c>
+      <c r="D131" t="s">
+        <v>40</v>
+      </c>
+      <c r="E131" t="s">
+        <v>103</v>
+      </c>
+      <c r="F131">
+        <v>31</v>
+      </c>
+      <c r="G131">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A132" s="2">
+        <v>46248</v>
+      </c>
+      <c r="B132" t="s">
+        <v>44</v>
+      </c>
+      <c r="C132" t="s">
+        <v>116</v>
+      </c>
+      <c r="D132" t="s">
+        <v>40</v>
+      </c>
+      <c r="E132" t="s">
+        <v>103</v>
+      </c>
+      <c r="F132">
+        <v>32</v>
+      </c>
+      <c r="G132">
+        <v>240</v>
       </c>
     </row>
   </sheetData>
@@ -3480,7 +3859,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D025E2E-BFF7-4E32-A03E-913AB4DFDB98}">
-  <dimension ref="A1:S216"/>
+  <dimension ref="A1:T216"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.6328125" customWidth="1"/>
@@ -3495,7 +3874,7 @@
     <col min="19" max="19" width="13.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="5" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:20" s="5" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>31</v>
       </c>
@@ -3553,8 +3932,11 @@
       <c r="S1" s="5" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="T1" s="5" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>42</v>
       </c>
@@ -3582,7 +3964,7 @@
       <c r="I2" s="6">
         <v>15.481199999999999</v>
       </c>
-      <c r="J2" s="12">
+      <c r="J2">
         <v>2</v>
       </c>
       <c r="K2">
@@ -3604,7 +3986,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>42</v>
       </c>
@@ -3632,7 +4014,7 @@
       <c r="I3" s="6">
         <v>15.481199999999999</v>
       </c>
-      <c r="J3" s="12">
+      <c r="J3">
         <v>2</v>
       </c>
       <c r="K3">
@@ -3657,7 +4039,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>43</v>
       </c>
@@ -3685,7 +4067,7 @@
       <c r="I4" s="6">
         <v>15.458</v>
       </c>
-      <c r="J4" s="12">
+      <c r="J4">
         <v>2</v>
       </c>
       <c r="K4">
@@ -3710,7 +4092,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>44</v>
       </c>
@@ -3738,7 +4120,7 @@
       <c r="I5" s="6">
         <v>15.3994</v>
       </c>
-      <c r="J5" s="12">
+      <c r="J5">
         <v>2</v>
       </c>
       <c r="K5">
@@ -3763,7 +4145,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>42</v>
       </c>
@@ -3791,7 +4173,7 @@
       <c r="I6" s="6">
         <v>15.481199999999999</v>
       </c>
-      <c r="J6" s="12">
+      <c r="J6">
         <v>1</v>
       </c>
       <c r="K6">
@@ -3813,7 +4195,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>43</v>
       </c>
@@ -3841,7 +4223,7 @@
       <c r="I7" s="6">
         <v>15.458</v>
       </c>
-      <c r="J7" s="12">
+      <c r="J7">
         <v>1</v>
       </c>
       <c r="K7">
@@ -3863,7 +4245,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>54</v>
       </c>
@@ -3891,7 +4273,7 @@
       <c r="I8" s="6">
         <v>15.7844</v>
       </c>
-      <c r="J8" s="12">
+      <c r="J8">
         <v>2</v>
       </c>
       <c r="K8">
@@ -3919,7 +4301,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>57</v>
       </c>
@@ -3947,7 +4329,7 @@
       <c r="I9" s="6">
         <v>15.738899999999999</v>
       </c>
-      <c r="J9" s="12">
+      <c r="J9">
         <v>1</v>
       </c>
       <c r="K9">
@@ -3972,7 +4354,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>58</v>
       </c>
@@ -4000,7 +4382,7 @@
       <c r="I10" s="6">
         <v>15.6995</v>
       </c>
-      <c r="J10" s="12">
+      <c r="J10">
         <v>2</v>
       </c>
       <c r="K10">
@@ -4025,7 +4407,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>59</v>
       </c>
@@ -4053,7 +4435,7 @@
       <c r="I11" s="6">
         <v>15.5815</v>
       </c>
-      <c r="J11" s="12">
+      <c r="J11">
         <v>1</v>
       </c>
       <c r="K11">
@@ -4078,7 +4460,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>54</v>
       </c>
@@ -4106,7 +4488,7 @@
       <c r="I12" s="6">
         <v>15.7844</v>
       </c>
-      <c r="J12" s="12">
+      <c r="J12">
         <v>2</v>
       </c>
       <c r="K12">
@@ -4131,7 +4513,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>73</v>
       </c>
@@ -4159,7 +4541,7 @@
       <c r="I13" s="6">
         <v>15.272</v>
       </c>
-      <c r="J13" s="12">
+      <c r="J13">
         <v>2</v>
       </c>
       <c r="K13" s="6">
@@ -4178,7 +4560,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>76</v>
       </c>
@@ -4206,7 +4588,7 @@
       <c r="I14" s="6">
         <v>15.217700000000001</v>
       </c>
-      <c r="J14" s="12">
+      <c r="J14">
         <v>3</v>
       </c>
       <c r="K14" s="6">
@@ -4225,7 +4607,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>77</v>
       </c>
@@ -4253,7 +4635,7 @@
       <c r="I15" s="6">
         <v>15.138999999999999</v>
       </c>
-      <c r="J15" s="12">
+      <c r="J15">
         <v>2</v>
       </c>
       <c r="K15" s="6">
@@ -4272,7 +4654,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>78</v>
       </c>
@@ -4300,7 +4682,7 @@
       <c r="I16" s="6">
         <v>15.414999999999999</v>
       </c>
-      <c r="J16" s="12">
+      <c r="J16">
         <v>3</v>
       </c>
       <c r="K16" s="6">
@@ -4347,7 +4729,7 @@
       <c r="I17" s="6">
         <v>15.481199999999999</v>
       </c>
-      <c r="J17" s="12">
+      <c r="J17">
         <v>2</v>
       </c>
       <c r="K17">
@@ -4394,7 +4776,7 @@
       <c r="I18" s="6">
         <v>15.481199999999999</v>
       </c>
-      <c r="J18" s="12">
+      <c r="J18">
         <v>1</v>
       </c>
       <c r="K18">
@@ -4444,7 +4826,7 @@
       <c r="I19" s="6">
         <v>15.3994</v>
       </c>
-      <c r="J19" s="12">
+      <c r="J19">
         <v>2</v>
       </c>
       <c r="K19">
@@ -4494,7 +4876,7 @@
       <c r="I20" s="6">
         <v>15.481199999999999</v>
       </c>
-      <c r="J20" s="12">
+      <c r="J20">
         <v>2</v>
       </c>
       <c r="K20">
@@ -4544,7 +4926,7 @@
       <c r="I21" s="6">
         <v>15.481199999999999</v>
       </c>
-      <c r="J21" s="12">
+      <c r="J21">
         <v>2</v>
       </c>
       <c r="K21">
@@ -4594,7 +4976,7 @@
       <c r="I22" s="6">
         <v>15.481199999999999</v>
       </c>
-      <c r="J22" s="12">
+      <c r="J22">
         <v>2</v>
       </c>
       <c r="K22">
@@ -4644,7 +5026,7 @@
       <c r="I23" s="6">
         <v>15.1264</v>
       </c>
-      <c r="J23" s="12">
+      <c r="J23">
         <v>4</v>
       </c>
       <c r="K23" s="6">
@@ -4668,7 +5050,7 @@
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="B24" t="s">
         <v>7</v>
@@ -4694,7 +5076,7 @@
       <c r="I24" s="6">
         <v>15.1318</v>
       </c>
-      <c r="J24" s="12">
+      <c r="J24">
         <v>4</v>
       </c>
       <c r="K24" s="6">
@@ -4750,7 +5132,7 @@
       <c r="I25" s="6">
         <v>15.3994</v>
       </c>
-      <c r="J25" s="12">
+      <c r="J25">
         <v>4</v>
       </c>
       <c r="K25" s="6">
@@ -4803,7 +5185,7 @@
       <c r="I26" s="6">
         <v>15.3994</v>
       </c>
-      <c r="J26" s="12">
+      <c r="J26">
         <v>4</v>
       </c>
       <c r="K26" s="6">
@@ -4859,7 +5241,7 @@
       <c r="I27" s="6">
         <v>15.7844</v>
       </c>
-      <c r="J27" s="12">
+      <c r="J27">
         <v>3</v>
       </c>
       <c r="K27">
@@ -4909,7 +5291,7 @@
       <c r="I28" s="6">
         <v>15.5144</v>
       </c>
-      <c r="J28" s="12">
+      <c r="J28">
         <v>4</v>
       </c>
       <c r="K28" s="6">
@@ -4959,7 +5341,7 @@
       <c r="I29" s="6">
         <v>15.481199999999999</v>
       </c>
-      <c r="J29" s="12">
+      <c r="J29">
         <v>3</v>
       </c>
       <c r="K29" s="6">
@@ -4988,7 +5370,7 @@
       </c>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A30" s="11" t="s">
+      <c r="A30" s="9" t="s">
         <v>97</v>
       </c>
       <c r="B30" t="s">
@@ -5015,7 +5397,7 @@
       <c r="I30" s="6">
         <v>15.6182</v>
       </c>
-      <c r="J30" s="12">
+      <c r="J30">
         <v>1</v>
       </c>
       <c r="K30" s="6">
@@ -5038,7 +5420,7 @@
       </c>
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A31" s="9" t="s">
+      <c r="A31" t="s">
         <v>97</v>
       </c>
       <c r="B31" t="s">
@@ -5065,7 +5447,7 @@
       <c r="I31" s="6">
         <v>15.6182</v>
       </c>
-      <c r="J31" s="12">
+      <c r="J31">
         <v>1</v>
       </c>
       <c r="K31" s="6">
@@ -5094,7 +5476,7 @@
       </c>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A32" s="9" t="s">
+      <c r="A32" t="s">
         <v>44</v>
       </c>
       <c r="B32" t="s">
@@ -5121,7 +5503,7 @@
       <c r="I32" s="6">
         <v>15.3994</v>
       </c>
-      <c r="J32" s="12">
+      <c r="J32">
         <v>1</v>
       </c>
       <c r="K32">
@@ -5143,8 +5525,8 @@
         <v>56</v>
       </c>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A33" s="9" t="s">
+    <row r="33" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
         <v>42</v>
       </c>
       <c r="B33" t="s">
@@ -5171,7 +5553,7 @@
       <c r="I33" s="6">
         <v>15.481199999999999</v>
       </c>
-      <c r="J33" s="12">
+      <c r="J33">
         <v>3</v>
       </c>
       <c r="K33" s="6">
@@ -5199,8 +5581,8 @@
         <v>56</v>
       </c>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A34" s="9" t="s">
+    <row r="34" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
         <v>44</v>
       </c>
       <c r="B34" t="s">
@@ -5227,7 +5609,7 @@
       <c r="I34" s="6">
         <v>15.3994</v>
       </c>
-      <c r="J34" s="12">
+      <c r="J34">
         <v>2</v>
       </c>
       <c r="K34" s="6">
@@ -5255,8 +5637,8 @@
         <v>99</v>
       </c>
     </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A35" s="9" t="s">
+    <row r="35" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
         <v>98</v>
       </c>
       <c r="B35" t="s">
@@ -5283,7 +5665,7 @@
       <c r="I35" s="6">
         <v>15.166399999999999</v>
       </c>
-      <c r="J35" s="12">
+      <c r="J35">
         <v>3</v>
       </c>
       <c r="K35" s="6">
@@ -5311,8 +5693,8 @@
         <v>99</v>
       </c>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A36" s="9" t="s">
+    <row r="36" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
         <v>44</v>
       </c>
       <c r="B36" t="s">
@@ -5339,7 +5721,7 @@
       <c r="I36" s="6">
         <v>15.3994</v>
       </c>
-      <c r="J36" s="12">
+      <c r="J36">
         <v>2</v>
       </c>
       <c r="K36">
@@ -5360,67 +5742,462 @@
       <c r="R36" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A37" s="9"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="3"/>
-      <c r="E37" s="3"/>
-    </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A38" s="9"/>
-      <c r="C38" s="4"/>
-      <c r="D38" s="3"/>
-      <c r="E38" s="3"/>
-    </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A39" s="9"/>
-      <c r="C39" s="4"/>
-      <c r="D39" s="3"/>
-      <c r="E39" s="3"/>
-    </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A40" s="9"/>
-      <c r="C40" s="4"/>
-      <c r="D40" s="3"/>
-      <c r="E40" s="3"/>
-    </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="C41" s="4"/>
-      <c r="D41" s="3"/>
-      <c r="E41" s="3"/>
-    </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="C42" s="4"/>
-      <c r="D42" s="3"/>
-      <c r="E42" s="3"/>
-    </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="C43" s="4"/>
-      <c r="D43" s="3"/>
-      <c r="E43" s="3"/>
-    </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="C44" s="4"/>
-      <c r="D44" s="3"/>
-      <c r="E44" s="3"/>
-    </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="S36" t="s">
+        <v>120</v>
+      </c>
+      <c r="T36" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>110</v>
+      </c>
+      <c r="B37" t="s">
+        <v>53</v>
+      </c>
+      <c r="C37" s="2">
+        <v>46243</v>
+      </c>
+      <c r="D37" s="3">
+        <v>0.72222222222222221</v>
+      </c>
+      <c r="E37" s="3">
+        <v>0.75</v>
+      </c>
+      <c r="F37" s="6">
+        <v>67.309799999999996</v>
+      </c>
+      <c r="G37" s="6">
+        <v>15.3231</v>
+      </c>
+      <c r="H37" s="6">
+        <v>67.309799999999996</v>
+      </c>
+      <c r="I37" s="6">
+        <v>15.3231</v>
+      </c>
+      <c r="J37" s="6">
+        <v>3</v>
+      </c>
+      <c r="K37" s="6">
+        <v>10</v>
+      </c>
+      <c r="L37" s="6">
+        <v>50</v>
+      </c>
+      <c r="M37" s="6">
+        <v>13.5</v>
+      </c>
+      <c r="N37" s="6">
+        <v>28</v>
+      </c>
+      <c r="O37" t="s">
+        <v>36</v>
+      </c>
+      <c r="P37" s="6">
+        <v>130</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>38</v>
+      </c>
+      <c r="R37" t="s">
+        <v>56</v>
+      </c>
+      <c r="T37" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>54</v>
+      </c>
+      <c r="B38" t="s">
+        <v>53</v>
+      </c>
+      <c r="C38" s="2">
+        <v>46243</v>
+      </c>
+      <c r="D38" s="3">
+        <v>0.76388888888888884</v>
+      </c>
+      <c r="E38" s="3">
+        <v>0.83680555555555558</v>
+      </c>
+      <c r="F38" s="6">
+        <v>67.5792</v>
+      </c>
+      <c r="G38" s="6">
+        <v>15.7844</v>
+      </c>
+      <c r="H38" s="7">
+        <v>67.5792</v>
+      </c>
+      <c r="I38" s="6">
+        <v>15.7844</v>
+      </c>
+      <c r="J38" s="6">
+        <v>3</v>
+      </c>
+      <c r="K38">
+        <v>20</v>
+      </c>
+      <c r="L38">
+        <v>40</v>
+      </c>
+      <c r="O38" t="s">
+        <v>36</v>
+      </c>
+      <c r="P38" s="6">
+        <v>161</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>38</v>
+      </c>
+      <c r="R38" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>112</v>
+      </c>
+      <c r="B39" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="2">
+        <v>46246</v>
+      </c>
+      <c r="D39" s="3">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="E39" s="3">
+        <v>0.43402777777777779</v>
+      </c>
+      <c r="F39" s="6">
+        <v>67.504000000000005</v>
+      </c>
+      <c r="G39" s="6">
+        <v>15.321400000000001</v>
+      </c>
+      <c r="H39" s="6">
+        <v>67.504000000000005</v>
+      </c>
+      <c r="I39" s="6">
+        <v>15.321400000000001</v>
+      </c>
+      <c r="J39" s="6">
+        <v>2</v>
+      </c>
+      <c r="K39" s="6">
+        <v>40</v>
+      </c>
+      <c r="L39" s="6">
+        <v>55</v>
+      </c>
+      <c r="M39" s="6">
+        <v>12.8</v>
+      </c>
+      <c r="N39" s="6">
+        <v>27.5</v>
+      </c>
+      <c r="O39" t="s">
+        <v>36</v>
+      </c>
+      <c r="P39" s="6">
+        <v>147</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>38</v>
+      </c>
+      <c r="R39" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>113</v>
+      </c>
+      <c r="B40" t="s">
+        <v>75</v>
+      </c>
+      <c r="C40" s="2">
+        <v>46246</v>
+      </c>
+      <c r="D40" s="3">
+        <v>0.46527777777777779</v>
+      </c>
+      <c r="E40" s="3">
+        <v>0.4861111111111111</v>
+      </c>
+      <c r="F40" s="6">
+        <v>67.493099999999998</v>
+      </c>
+      <c r="G40" s="6">
+        <v>15.1549</v>
+      </c>
+      <c r="H40" s="6">
+        <v>67.493099999999998</v>
+      </c>
+      <c r="I40" s="6">
+        <v>15.1549</v>
+      </c>
+      <c r="J40" s="6">
+        <v>1</v>
+      </c>
+      <c r="K40" s="6">
+        <v>20</v>
+      </c>
+      <c r="L40" s="6">
+        <v>30</v>
+      </c>
+      <c r="O40" t="s">
+        <v>36</v>
+      </c>
+      <c r="P40" s="6">
+        <v>244</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>38</v>
+      </c>
+      <c r="R40" t="s">
+        <v>56</v>
+      </c>
+      <c r="T40" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>115</v>
+      </c>
+      <c r="B41" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="2">
+        <v>46246</v>
+      </c>
+      <c r="D41" s="3">
+        <v>0.61111111111111116</v>
+      </c>
+      <c r="E41" s="3">
+        <v>0.61805555555555558</v>
+      </c>
+      <c r="F41" s="6">
+        <v>67.349299999999999</v>
+      </c>
+      <c r="G41" s="6">
+        <v>15.1318</v>
+      </c>
+      <c r="H41" s="6">
+        <v>67.349299999999999</v>
+      </c>
+      <c r="I41" s="6">
+        <v>15.1318</v>
+      </c>
+      <c r="J41" s="6">
+        <v>1</v>
+      </c>
+      <c r="K41" s="6">
+        <v>15</v>
+      </c>
+      <c r="L41" s="6">
+        <v>35</v>
+      </c>
+      <c r="O41" t="s">
+        <v>55</v>
+      </c>
+      <c r="P41" s="6">
+        <v>246</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>38</v>
+      </c>
+      <c r="R41" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="42" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>44</v>
+      </c>
+      <c r="B42" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="2">
+        <v>46247</v>
+      </c>
+      <c r="D42" s="3">
+        <v>0.35416666666666669</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0.4861111111111111</v>
+      </c>
+      <c r="F42" s="6">
+        <v>67.503900000000002</v>
+      </c>
+      <c r="G42" s="6">
+        <v>15.3994</v>
+      </c>
+      <c r="H42" s="6">
+        <v>67.503900000000002</v>
+      </c>
+      <c r="I42" s="6">
+        <v>15.3994</v>
+      </c>
+      <c r="J42" s="6">
+        <v>2</v>
+      </c>
+      <c r="K42" s="6">
+        <v>25</v>
+      </c>
+      <c r="L42" s="6">
+        <v>50</v>
+      </c>
+      <c r="O42" t="s">
+        <v>36</v>
+      </c>
+      <c r="P42" s="6">
+        <v>130</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>38</v>
+      </c>
+      <c r="R42" t="s">
+        <v>56</v>
+      </c>
+      <c r="S42" t="s">
+        <v>121</v>
+      </c>
+      <c r="T42" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="43" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>42</v>
+      </c>
+      <c r="B43" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="2">
+        <v>46247</v>
+      </c>
+      <c r="D43" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="E43" s="3">
+        <v>0.52777777777777779</v>
+      </c>
+      <c r="F43" s="6">
+        <v>67.516000000000005</v>
+      </c>
+      <c r="G43" s="6">
+        <v>15.481199999999999</v>
+      </c>
+      <c r="H43" s="6">
+        <v>67.516000000000005</v>
+      </c>
+      <c r="I43" s="6">
+        <v>15.481199999999999</v>
+      </c>
+      <c r="J43" s="6">
+        <v>2</v>
+      </c>
+      <c r="K43">
+        <v>15</v>
+      </c>
+      <c r="L43">
+        <v>25</v>
+      </c>
+      <c r="O43" t="s">
+        <v>36</v>
+      </c>
+      <c r="P43" s="6">
+        <v>250</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>38</v>
+      </c>
+      <c r="R43" t="s">
+        <v>56</v>
+      </c>
+      <c r="T43" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="44" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>44</v>
+      </c>
+      <c r="B44" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="2">
+        <v>46248</v>
+      </c>
+      <c r="D44" s="3">
+        <v>0.3125</v>
+      </c>
+      <c r="E44" s="3">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="F44" s="6">
+        <v>67.503900000000002</v>
+      </c>
+      <c r="G44" s="6">
+        <v>15.3994</v>
+      </c>
+      <c r="H44" s="6">
+        <v>67.503900000000002</v>
+      </c>
+      <c r="I44" s="6">
+        <v>15.3994</v>
+      </c>
+      <c r="J44" s="6">
+        <v>2</v>
+      </c>
+      <c r="K44" s="6">
+        <v>25</v>
+      </c>
+      <c r="L44" s="6">
+        <v>50</v>
+      </c>
+      <c r="O44" t="s">
+        <v>36</v>
+      </c>
+      <c r="P44" s="6">
+        <v>100</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>38</v>
+      </c>
+      <c r="R44" t="s">
+        <v>56</v>
+      </c>
+      <c r="S44" t="s">
+        <v>122</v>
+      </c>
+      <c r="T44" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="45" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C45" s="4"/>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
     </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C46" s="4"/>
       <c r="D46" s="3"/>
       <c r="E46" s="3"/>
     </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C47" s="4"/>
       <c r="D47" s="3"/>
       <c r="E47" s="3"/>
     </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C48" s="4"/>
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>

--- a/Survey_data_real.xlsx
+++ b/Survey_data_real.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop (1)\Other\ShinyAPPnorway\ACCESS-FjordAPP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F496B0B-A355-47C3-814C-0C56738B4DC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{734DDD04-CCB8-47BC-B11D-362EF8DBCC84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="catchdata" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="830" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1093" uniqueCount="140">
   <si>
     <t>Date</t>
   </si>
@@ -406,6 +406,57 @@
   </si>
   <si>
     <t>lost 2/3 halibut</t>
+  </si>
+  <si>
+    <t>Brattlia</t>
+  </si>
+  <si>
+    <t>Wavy</t>
+  </si>
+  <si>
+    <t>Deep fish</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>Øygårdsskjæret</t>
+  </si>
+  <si>
+    <t>Simone</t>
+  </si>
+  <si>
+    <t>Thomas</t>
+  </si>
+  <si>
+    <t>Rossana</t>
+  </si>
+  <si>
+    <t>salento_fishing_team</t>
+  </si>
+  <si>
+    <t>tommi_cdl_</t>
+  </si>
+  <si>
+    <t>muccafru</t>
+  </si>
+  <si>
+    <t>Massimo</t>
+  </si>
+  <si>
+    <t>2 otholits</t>
+  </si>
+  <si>
+    <t>crustacean gammarus?</t>
+  </si>
+  <si>
+    <t>Grey gurnard</t>
+  </si>
+  <si>
+    <t>fish rest and thalassinidea</t>
+  </si>
+  <si>
+    <t>Crab munida rugosa</t>
   </si>
 </sst>
 </file>
@@ -784,7 +835,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J132"/>
+  <dimension ref="A1:J180"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="25.7265625" style="2" customWidth="1"/>
@@ -3844,6 +3895,1179 @@
       </c>
       <c r="G132">
         <v>240</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A133" s="2">
+        <v>46251</v>
+      </c>
+      <c r="B133" t="s">
+        <v>42</v>
+      </c>
+      <c r="C133" t="s">
+        <v>128</v>
+      </c>
+      <c r="D133" t="s">
+        <v>40</v>
+      </c>
+      <c r="E133" t="s">
+        <v>103</v>
+      </c>
+      <c r="F133">
+        <v>37</v>
+      </c>
+      <c r="G133">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A134" s="2">
+        <v>46251</v>
+      </c>
+      <c r="B134" t="s">
+        <v>42</v>
+      </c>
+      <c r="C134" t="s">
+        <v>128</v>
+      </c>
+      <c r="D134" t="s">
+        <v>40</v>
+      </c>
+      <c r="E134" t="s">
+        <v>103</v>
+      </c>
+      <c r="F134">
+        <v>32</v>
+      </c>
+      <c r="G134">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A135" s="2">
+        <v>46251</v>
+      </c>
+      <c r="B135" t="s">
+        <v>42</v>
+      </c>
+      <c r="C135" t="s">
+        <v>129</v>
+      </c>
+      <c r="D135" t="s">
+        <v>40</v>
+      </c>
+      <c r="E135" t="s">
+        <v>103</v>
+      </c>
+      <c r="F135">
+        <v>32</v>
+      </c>
+      <c r="G135">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A136" s="2">
+        <v>46251</v>
+      </c>
+      <c r="B136" t="s">
+        <v>42</v>
+      </c>
+      <c r="C136" t="s">
+        <v>129</v>
+      </c>
+      <c r="D136" t="s">
+        <v>40</v>
+      </c>
+      <c r="E136" t="s">
+        <v>83</v>
+      </c>
+      <c r="F136">
+        <v>38</v>
+      </c>
+      <c r="G136">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="137" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A137" s="2">
+        <v>46251</v>
+      </c>
+      <c r="B137" t="s">
+        <v>42</v>
+      </c>
+      <c r="C137" t="s">
+        <v>129</v>
+      </c>
+      <c r="D137" t="s">
+        <v>40</v>
+      </c>
+      <c r="E137" t="s">
+        <v>103</v>
+      </c>
+      <c r="F137">
+        <v>35</v>
+      </c>
+      <c r="G137">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A138" s="2">
+        <v>46251</v>
+      </c>
+      <c r="B138" t="s">
+        <v>42</v>
+      </c>
+      <c r="C138" t="s">
+        <v>130</v>
+      </c>
+      <c r="D138" t="s">
+        <v>40</v>
+      </c>
+      <c r="E138" t="s">
+        <v>83</v>
+      </c>
+      <c r="F138">
+        <v>40</v>
+      </c>
+      <c r="G138">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A139" s="2">
+        <v>46251</v>
+      </c>
+      <c r="B139" t="s">
+        <v>42</v>
+      </c>
+      <c r="C139" t="s">
+        <v>130</v>
+      </c>
+      <c r="D139" t="s">
+        <v>40</v>
+      </c>
+      <c r="E139" t="s">
+        <v>83</v>
+      </c>
+      <c r="F139">
+        <v>50</v>
+      </c>
+      <c r="G139">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="140" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A140" s="2">
+        <v>46251</v>
+      </c>
+      <c r="B140" t="s">
+        <v>42</v>
+      </c>
+      <c r="C140" t="s">
+        <v>128</v>
+      </c>
+      <c r="D140" t="s">
+        <v>40</v>
+      </c>
+      <c r="E140" t="s">
+        <v>6</v>
+      </c>
+      <c r="F140">
+        <v>59</v>
+      </c>
+      <c r="G140">
+        <v>1880</v>
+      </c>
+    </row>
+    <row r="141" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A141" s="2">
+        <v>46251</v>
+      </c>
+      <c r="B141" t="s">
+        <v>44</v>
+      </c>
+      <c r="C141" t="s">
+        <v>129</v>
+      </c>
+      <c r="D141" t="s">
+        <v>40</v>
+      </c>
+      <c r="E141" t="s">
+        <v>103</v>
+      </c>
+      <c r="F141">
+        <v>32</v>
+      </c>
+      <c r="G141">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="142" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A142" s="2">
+        <v>46251</v>
+      </c>
+      <c r="B142" t="s">
+        <v>44</v>
+      </c>
+      <c r="C142" t="s">
+        <v>129</v>
+      </c>
+      <c r="D142" t="s">
+        <v>40</v>
+      </c>
+      <c r="E142" t="s">
+        <v>103</v>
+      </c>
+      <c r="F142">
+        <v>41.5</v>
+      </c>
+      <c r="G142">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="143" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A143" s="2">
+        <v>46251</v>
+      </c>
+      <c r="B143" t="s">
+        <v>44</v>
+      </c>
+      <c r="C143" t="s">
+        <v>129</v>
+      </c>
+      <c r="D143" t="s">
+        <v>40</v>
+      </c>
+      <c r="E143" t="s">
+        <v>103</v>
+      </c>
+      <c r="F143">
+        <v>30</v>
+      </c>
+      <c r="I143" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="144" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A144" s="2">
+        <v>46251</v>
+      </c>
+      <c r="B144" t="s">
+        <v>44</v>
+      </c>
+      <c r="C144" t="s">
+        <v>129</v>
+      </c>
+      <c r="D144" t="s">
+        <v>40</v>
+      </c>
+      <c r="E144" t="s">
+        <v>103</v>
+      </c>
+      <c r="F144">
+        <v>30</v>
+      </c>
+      <c r="I144" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="145" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A145" s="2">
+        <v>46251</v>
+      </c>
+      <c r="B145" t="s">
+        <v>44</v>
+      </c>
+      <c r="C145" t="s">
+        <v>129</v>
+      </c>
+      <c r="D145" t="s">
+        <v>40</v>
+      </c>
+      <c r="E145" t="s">
+        <v>103</v>
+      </c>
+      <c r="F145">
+        <v>30</v>
+      </c>
+      <c r="I145" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="146" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A146" s="2">
+        <v>46251</v>
+      </c>
+      <c r="B146" t="s">
+        <v>44</v>
+      </c>
+      <c r="C146" t="s">
+        <v>128</v>
+      </c>
+      <c r="D146" t="s">
+        <v>40</v>
+      </c>
+      <c r="E146" t="s">
+        <v>103</v>
+      </c>
+      <c r="F146">
+        <v>30</v>
+      </c>
+      <c r="I146" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="147" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A147" s="2">
+        <v>46251</v>
+      </c>
+      <c r="B147" t="s">
+        <v>44</v>
+      </c>
+      <c r="C147" t="s">
+        <v>128</v>
+      </c>
+      <c r="D147" t="s">
+        <v>40</v>
+      </c>
+      <c r="E147" t="s">
+        <v>6</v>
+      </c>
+      <c r="F147">
+        <v>76</v>
+      </c>
+      <c r="G147">
+        <v>2850</v>
+      </c>
+    </row>
+    <row r="148" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A148" s="2">
+        <v>46257</v>
+      </c>
+      <c r="B148" t="s">
+        <v>110</v>
+      </c>
+      <c r="C148" t="s">
+        <v>131</v>
+      </c>
+      <c r="D148" t="s">
+        <v>40</v>
+      </c>
+      <c r="E148" t="s">
+        <v>79</v>
+      </c>
+      <c r="F148">
+        <v>48</v>
+      </c>
+      <c r="G148">
+        <v>1000</v>
+      </c>
+      <c r="J148" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="149" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A149" s="2">
+        <v>46257</v>
+      </c>
+      <c r="B149" t="s">
+        <v>110</v>
+      </c>
+      <c r="C149" t="s">
+        <v>133</v>
+      </c>
+      <c r="D149" t="s">
+        <v>40</v>
+      </c>
+      <c r="E149" t="s">
+        <v>103</v>
+      </c>
+      <c r="F149">
+        <v>26</v>
+      </c>
+      <c r="G149">
+        <v>55</v>
+      </c>
+      <c r="H149" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="150" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A150" s="2">
+        <v>46257</v>
+      </c>
+      <c r="B150" t="s">
+        <v>123</v>
+      </c>
+      <c r="C150" t="s">
+        <v>133</v>
+      </c>
+      <c r="D150" t="s">
+        <v>40</v>
+      </c>
+      <c r="E150" t="s">
+        <v>6</v>
+      </c>
+      <c r="F150">
+        <v>38</v>
+      </c>
+      <c r="G150">
+        <v>445</v>
+      </c>
+      <c r="I150" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="151" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A151" s="2">
+        <v>46257</v>
+      </c>
+      <c r="B151" t="s">
+        <v>123</v>
+      </c>
+      <c r="C151" t="s">
+        <v>131</v>
+      </c>
+      <c r="D151" t="s">
+        <v>40</v>
+      </c>
+      <c r="E151" t="s">
+        <v>83</v>
+      </c>
+      <c r="F151">
+        <v>51</v>
+      </c>
+      <c r="G151">
+        <v>1170</v>
+      </c>
+      <c r="J151" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="152" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A152" s="2">
+        <v>46257</v>
+      </c>
+      <c r="B152" t="s">
+        <v>123</v>
+      </c>
+      <c r="C152" t="s">
+        <v>132</v>
+      </c>
+      <c r="D152" t="s">
+        <v>40</v>
+      </c>
+      <c r="E152" t="s">
+        <v>103</v>
+      </c>
+      <c r="F152">
+        <v>40</v>
+      </c>
+      <c r="G152">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="153" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A153" s="2">
+        <v>46257</v>
+      </c>
+      <c r="B153" t="s">
+        <v>123</v>
+      </c>
+      <c r="C153" t="s">
+        <v>133</v>
+      </c>
+      <c r="D153" t="s">
+        <v>40</v>
+      </c>
+      <c r="E153" t="s">
+        <v>79</v>
+      </c>
+      <c r="F153">
+        <v>61</v>
+      </c>
+      <c r="G153">
+        <v>1000</v>
+      </c>
+      <c r="I153" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="154" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A154" s="2">
+        <v>46257</v>
+      </c>
+      <c r="B154" t="s">
+        <v>123</v>
+      </c>
+      <c r="C154" t="s">
+        <v>132</v>
+      </c>
+      <c r="D154" t="s">
+        <v>40</v>
+      </c>
+      <c r="E154" t="s">
+        <v>6</v>
+      </c>
+      <c r="F154">
+        <v>41</v>
+      </c>
+      <c r="G154">
+        <v>750</v>
+      </c>
+      <c r="I154" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="155" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A155" s="2">
+        <v>46257</v>
+      </c>
+      <c r="B155" t="s">
+        <v>123</v>
+      </c>
+      <c r="C155" t="s">
+        <v>131</v>
+      </c>
+      <c r="D155" t="s">
+        <v>40</v>
+      </c>
+      <c r="E155" t="s">
+        <v>83</v>
+      </c>
+      <c r="F155">
+        <v>56</v>
+      </c>
+      <c r="G155">
+        <v>1600</v>
+      </c>
+      <c r="J155" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="156" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A156" s="2">
+        <v>46257</v>
+      </c>
+      <c r="B156" t="s">
+        <v>123</v>
+      </c>
+      <c r="C156" t="s">
+        <v>134</v>
+      </c>
+      <c r="D156" t="s">
+        <v>40</v>
+      </c>
+      <c r="E156" t="s">
+        <v>79</v>
+      </c>
+      <c r="F156">
+        <v>57</v>
+      </c>
+      <c r="G156">
+        <v>1415</v>
+      </c>
+      <c r="I156" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="157" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A157" s="2">
+        <v>46257</v>
+      </c>
+      <c r="B157" t="s">
+        <v>123</v>
+      </c>
+      <c r="C157" t="s">
+        <v>132</v>
+      </c>
+      <c r="D157" t="s">
+        <v>40</v>
+      </c>
+      <c r="E157" t="s">
+        <v>79</v>
+      </c>
+      <c r="F157">
+        <v>52</v>
+      </c>
+      <c r="G157">
+        <v>1400</v>
+      </c>
+      <c r="I157" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="158" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A158" s="2">
+        <v>46257</v>
+      </c>
+      <c r="B158" t="s">
+        <v>123</v>
+      </c>
+      <c r="C158" t="s">
+        <v>132</v>
+      </c>
+      <c r="D158" t="s">
+        <v>40</v>
+      </c>
+      <c r="E158" t="s">
+        <v>83</v>
+      </c>
+      <c r="F158">
+        <v>55</v>
+      </c>
+      <c r="G158">
+        <v>1605</v>
+      </c>
+      <c r="I158" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="159" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A159" s="2">
+        <v>46257</v>
+      </c>
+      <c r="B159" t="s">
+        <v>123</v>
+      </c>
+      <c r="C159" t="s">
+        <v>131</v>
+      </c>
+      <c r="D159" t="s">
+        <v>40</v>
+      </c>
+      <c r="E159" t="s">
+        <v>83</v>
+      </c>
+      <c r="F159">
+        <v>48</v>
+      </c>
+      <c r="G159">
+        <v>1003</v>
+      </c>
+      <c r="I159" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="160" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A160" s="2">
+        <v>46257</v>
+      </c>
+      <c r="B160" t="s">
+        <v>123</v>
+      </c>
+      <c r="C160" t="s">
+        <v>131</v>
+      </c>
+      <c r="D160" t="s">
+        <v>40</v>
+      </c>
+      <c r="E160" t="s">
+        <v>83</v>
+      </c>
+      <c r="F160">
+        <v>28</v>
+      </c>
+      <c r="G160">
+        <v>225</v>
+      </c>
+      <c r="H160" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="161" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A161" s="2">
+        <v>46257</v>
+      </c>
+      <c r="B161" t="s">
+        <v>54</v>
+      </c>
+      <c r="C161" t="s">
+        <v>132</v>
+      </c>
+      <c r="D161" t="s">
+        <v>40</v>
+      </c>
+      <c r="E161" t="s">
+        <v>6</v>
+      </c>
+      <c r="F161">
+        <v>58</v>
+      </c>
+      <c r="G161">
+        <v>1480</v>
+      </c>
+      <c r="H161" t="s">
+        <v>119</v>
+      </c>
+      <c r="J161" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="162" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A162" s="2">
+        <v>46257</v>
+      </c>
+      <c r="B162" t="s">
+        <v>54</v>
+      </c>
+      <c r="C162" t="s">
+        <v>131</v>
+      </c>
+      <c r="D162" t="s">
+        <v>40</v>
+      </c>
+      <c r="E162" t="s">
+        <v>83</v>
+      </c>
+      <c r="F162">
+        <v>57</v>
+      </c>
+      <c r="G162">
+        <v>1455</v>
+      </c>
+      <c r="I162" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="163" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A163" s="2">
+        <v>46257</v>
+      </c>
+      <c r="B163" t="s">
+        <v>54</v>
+      </c>
+      <c r="C163" t="s">
+        <v>131</v>
+      </c>
+      <c r="D163" t="s">
+        <v>96</v>
+      </c>
+      <c r="E163" t="s">
+        <v>68</v>
+      </c>
+      <c r="F163">
+        <v>109</v>
+      </c>
+      <c r="G163">
+        <v>14830</v>
+      </c>
+    </row>
+    <row r="164" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A164" s="2">
+        <v>46257</v>
+      </c>
+      <c r="B164" t="s">
+        <v>54</v>
+      </c>
+      <c r="C164" t="s">
+        <v>131</v>
+      </c>
+      <c r="D164" t="s">
+        <v>40</v>
+      </c>
+      <c r="E164" t="s">
+        <v>137</v>
+      </c>
+      <c r="F164">
+        <v>36</v>
+      </c>
+      <c r="G164">
+        <v>420</v>
+      </c>
+      <c r="I164" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="165" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A165" s="2">
+        <v>46257</v>
+      </c>
+      <c r="B165" t="s">
+        <v>54</v>
+      </c>
+      <c r="C165" t="s">
+        <v>131</v>
+      </c>
+      <c r="D165" t="s">
+        <v>96</v>
+      </c>
+      <c r="E165" t="s">
+        <v>68</v>
+      </c>
+      <c r="F165">
+        <v>70</v>
+      </c>
+      <c r="G165">
+        <v>3000</v>
+      </c>
+      <c r="I165" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="166" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A166" s="2">
+        <v>46257</v>
+      </c>
+      <c r="B166" t="s">
+        <v>54</v>
+      </c>
+      <c r="C166" t="s">
+        <v>132</v>
+      </c>
+      <c r="D166" t="s">
+        <v>40</v>
+      </c>
+      <c r="E166" t="s">
+        <v>79</v>
+      </c>
+      <c r="F166">
+        <v>57</v>
+      </c>
+      <c r="G166">
+        <v>1601</v>
+      </c>
+      <c r="I166" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="167" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A167" s="2">
+        <v>46257</v>
+      </c>
+      <c r="B167" t="s">
+        <v>54</v>
+      </c>
+      <c r="C167" t="s">
+        <v>131</v>
+      </c>
+      <c r="D167" t="s">
+        <v>40</v>
+      </c>
+      <c r="E167" t="s">
+        <v>79</v>
+      </c>
+      <c r="F167">
+        <v>74</v>
+      </c>
+      <c r="G167">
+        <v>2105</v>
+      </c>
+    </row>
+    <row r="168" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A168" s="2">
+        <v>46257</v>
+      </c>
+      <c r="B168" t="s">
+        <v>54</v>
+      </c>
+      <c r="C168" t="s">
+        <v>132</v>
+      </c>
+      <c r="D168" t="s">
+        <v>40</v>
+      </c>
+      <c r="E168" t="s">
+        <v>79</v>
+      </c>
+      <c r="F168">
+        <v>59</v>
+      </c>
+      <c r="G168">
+        <v>1870</v>
+      </c>
+      <c r="I168" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="169" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A169" s="2">
+        <v>46259</v>
+      </c>
+      <c r="B169" t="s">
+        <v>97</v>
+      </c>
+      <c r="C169" t="s">
+        <v>86</v>
+      </c>
+      <c r="D169" t="s">
+        <v>60</v>
+      </c>
+      <c r="E169" t="s">
+        <v>83</v>
+      </c>
+      <c r="F169">
+        <v>63</v>
+      </c>
+      <c r="G169">
+        <v>2040</v>
+      </c>
+    </row>
+    <row r="170" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A170" s="2">
+        <v>46259</v>
+      </c>
+      <c r="B170" t="s">
+        <v>97</v>
+      </c>
+      <c r="C170" t="s">
+        <v>132</v>
+      </c>
+      <c r="D170" t="s">
+        <v>41</v>
+      </c>
+      <c r="E170" t="s">
+        <v>6</v>
+      </c>
+      <c r="F170">
+        <v>69</v>
+      </c>
+      <c r="G170">
+        <v>2600</v>
+      </c>
+      <c r="I170" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="171" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A171" s="2">
+        <v>46259</v>
+      </c>
+      <c r="B171" t="s">
+        <v>97</v>
+      </c>
+      <c r="C171" t="s">
+        <v>132</v>
+      </c>
+      <c r="D171" t="s">
+        <v>40</v>
+      </c>
+      <c r="E171" t="s">
+        <v>83</v>
+      </c>
+      <c r="F171">
+        <v>66</v>
+      </c>
+      <c r="G171">
+        <v>2150</v>
+      </c>
+    </row>
+    <row r="172" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A172" s="2">
+        <v>46259</v>
+      </c>
+      <c r="B172" t="s">
+        <v>97</v>
+      </c>
+      <c r="C172" t="s">
+        <v>131</v>
+      </c>
+      <c r="D172" t="s">
+        <v>40</v>
+      </c>
+      <c r="E172" t="s">
+        <v>83</v>
+      </c>
+      <c r="F172">
+        <v>68</v>
+      </c>
+      <c r="G172">
+        <v>2180</v>
+      </c>
+    </row>
+    <row r="173" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A173" s="2">
+        <v>46259</v>
+      </c>
+      <c r="B173" t="s">
+        <v>97</v>
+      </c>
+      <c r="C173" t="s">
+        <v>131</v>
+      </c>
+      <c r="D173" t="s">
+        <v>40</v>
+      </c>
+      <c r="E173" t="s">
+        <v>83</v>
+      </c>
+      <c r="F173">
+        <v>67</v>
+      </c>
+      <c r="G173">
+        <v>2200</v>
+      </c>
+      <c r="I173" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="174" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A174" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B174" t="s">
+        <v>112</v>
+      </c>
+      <c r="C174" t="s">
+        <v>131</v>
+      </c>
+      <c r="D174" t="s">
+        <v>40</v>
+      </c>
+      <c r="E174" t="s">
+        <v>103</v>
+      </c>
+      <c r="F174">
+        <v>41</v>
+      </c>
+      <c r="G174">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="175" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A175" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B175" t="s">
+        <v>112</v>
+      </c>
+      <c r="C175" t="s">
+        <v>132</v>
+      </c>
+      <c r="D175" t="s">
+        <v>40</v>
+      </c>
+      <c r="E175" t="s">
+        <v>103</v>
+      </c>
+      <c r="F175">
+        <v>43</v>
+      </c>
+      <c r="G175">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="176" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A176" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B176" t="s">
+        <v>112</v>
+      </c>
+      <c r="C176" t="s">
+        <v>133</v>
+      </c>
+      <c r="D176" t="s">
+        <v>40</v>
+      </c>
+      <c r="E176" t="s">
+        <v>103</v>
+      </c>
+      <c r="F176">
+        <v>37</v>
+      </c>
+      <c r="G176">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="177" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A177" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B177" t="s">
+        <v>112</v>
+      </c>
+      <c r="C177" t="s">
+        <v>132</v>
+      </c>
+      <c r="D177" t="s">
+        <v>96</v>
+      </c>
+      <c r="E177" t="s">
+        <v>61</v>
+      </c>
+      <c r="F177">
+        <v>55</v>
+      </c>
+      <c r="G177">
+        <v>1785</v>
+      </c>
+      <c r="J177" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="178" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A178" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B178" t="s">
+        <v>112</v>
+      </c>
+      <c r="C178" t="s">
+        <v>131</v>
+      </c>
+      <c r="D178" t="s">
+        <v>60</v>
+      </c>
+      <c r="E178" t="s">
+        <v>61</v>
+      </c>
+      <c r="F178">
+        <v>58</v>
+      </c>
+      <c r="G178">
+        <v>2265</v>
+      </c>
+    </row>
+    <row r="179" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A179" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B179" t="s">
+        <v>127</v>
+      </c>
+      <c r="C179" t="s">
+        <v>131</v>
+      </c>
+      <c r="D179" t="s">
+        <v>40</v>
+      </c>
+      <c r="E179" t="s">
+        <v>79</v>
+      </c>
+      <c r="F179">
+        <v>67</v>
+      </c>
+      <c r="G179">
+        <v>2550</v>
+      </c>
+    </row>
+    <row r="180" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A180" s="2">
+        <v>46260</v>
+      </c>
+      <c r="B180" t="s">
+        <v>127</v>
+      </c>
+      <c r="C180" t="s">
+        <v>131</v>
+      </c>
+      <c r="D180" t="s">
+        <v>40</v>
+      </c>
+      <c r="E180" t="s">
+        <v>61</v>
+      </c>
+      <c r="F180">
+        <v>45</v>
+      </c>
+      <c r="G180">
+        <v>900</v>
+      </c>
+      <c r="H180" t="s">
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -5766,16 +6990,16 @@
         <v>0.75</v>
       </c>
       <c r="F37" s="6">
-        <v>67.309799999999996</v>
+        <v>67.516900000000007</v>
       </c>
       <c r="G37" s="6">
-        <v>15.3231</v>
+        <v>15.5364</v>
       </c>
       <c r="H37" s="6">
-        <v>67.309799999999996</v>
+        <v>67.516900000000007</v>
       </c>
       <c r="I37" s="6">
-        <v>15.3231</v>
+        <v>15.5364</v>
       </c>
       <c r="J37" s="6">
         <v>3</v>
@@ -5863,7 +7087,7 @@
         <v>112</v>
       </c>
       <c r="B39" t="s">
-        <v>7</v>
+        <v>75</v>
       </c>
       <c r="C39" s="2">
         <v>46246</v>
@@ -6183,101 +7407,497 @@
       </c>
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="C45" s="4"/>
-      <c r="D45" s="3"/>
-      <c r="E45" s="3"/>
+      <c r="A45" t="s">
+        <v>42</v>
+      </c>
+      <c r="B45" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="2">
+        <v>46251</v>
+      </c>
+      <c r="D45" s="3">
+        <v>0.39166666666666666</v>
+      </c>
+      <c r="E45" s="3">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="F45" s="6">
+        <v>67.516000000000005</v>
+      </c>
+      <c r="G45" s="6">
+        <v>15.481199999999999</v>
+      </c>
+      <c r="H45" s="6">
+        <v>67.516000000000005</v>
+      </c>
+      <c r="I45" s="6">
+        <v>15.481199999999999</v>
+      </c>
+      <c r="J45" s="6">
+        <v>4</v>
+      </c>
+      <c r="K45">
+        <v>20</v>
+      </c>
+      <c r="L45">
+        <v>40</v>
+      </c>
+      <c r="M45" s="6">
+        <v>13.8</v>
+      </c>
+      <c r="N45" s="6">
+        <v>27.5</v>
+      </c>
+      <c r="O45" t="s">
+        <v>55</v>
+      </c>
+      <c r="P45" s="6">
+        <v>67</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>38</v>
+      </c>
+      <c r="R45" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="C46" s="4"/>
-      <c r="D46" s="3"/>
-      <c r="E46" s="3"/>
+      <c r="A46" t="s">
+        <v>44</v>
+      </c>
+      <c r="B46" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" s="2">
+        <v>46251</v>
+      </c>
+      <c r="D46" s="3">
+        <v>0.46875</v>
+      </c>
+      <c r="E46" s="3">
+        <v>0.54861111111111116</v>
+      </c>
+      <c r="F46" s="6">
+        <v>67.503900000000002</v>
+      </c>
+      <c r="G46" s="6">
+        <v>15.3994</v>
+      </c>
+      <c r="H46" s="6">
+        <v>67.503900000000002</v>
+      </c>
+      <c r="I46" s="6">
+        <v>15.3994</v>
+      </c>
+      <c r="J46" s="6">
+        <v>4</v>
+      </c>
+      <c r="K46" s="6">
+        <v>20</v>
+      </c>
+      <c r="L46" s="6">
+        <v>45</v>
+      </c>
+      <c r="M46" s="6">
+        <v>13.8</v>
+      </c>
+      <c r="N46" s="6">
+        <v>27.5</v>
+      </c>
+      <c r="O46" t="s">
+        <v>36</v>
+      </c>
+      <c r="P46" s="6">
+        <v>89</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>38</v>
+      </c>
+      <c r="R46" t="s">
+        <v>56</v>
+      </c>
     </row>
     <row r="47" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="C47" s="4"/>
-      <c r="D47" s="3"/>
-      <c r="E47" s="3"/>
+      <c r="A47" t="s">
+        <v>110</v>
+      </c>
+      <c r="B47" t="s">
+        <v>53</v>
+      </c>
+      <c r="C47" s="2">
+        <v>46257</v>
+      </c>
+      <c r="D47" s="3">
+        <v>0.44930555555555557</v>
+      </c>
+      <c r="E47" s="3">
+        <v>0.47222222222222221</v>
+      </c>
+      <c r="F47" s="6">
+        <v>67.516900000000007</v>
+      </c>
+      <c r="G47" s="6">
+        <v>15.5364</v>
+      </c>
+      <c r="H47" s="6">
+        <v>67.516900000000007</v>
+      </c>
+      <c r="I47" s="6">
+        <v>15.5364</v>
+      </c>
+      <c r="J47" s="6">
+        <v>3</v>
+      </c>
+      <c r="K47" s="6">
+        <v>15</v>
+      </c>
+      <c r="L47" s="6">
+        <v>25</v>
+      </c>
+      <c r="M47" s="6">
+        <v>14.5</v>
+      </c>
+      <c r="N47" s="6">
+        <v>27</v>
+      </c>
+      <c r="O47" t="s">
+        <v>37</v>
+      </c>
+      <c r="P47" s="6">
+        <v>209</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>38</v>
+      </c>
+      <c r="R47" t="s">
+        <v>56</v>
+      </c>
+      <c r="T47" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="48" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="C48" s="4"/>
-      <c r="D48" s="3"/>
-      <c r="E48" s="3"/>
-    </row>
-    <row r="49" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C49" s="4"/>
-      <c r="D49" s="3"/>
-      <c r="E49" s="3"/>
-    </row>
-    <row r="50" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C50" s="4"/>
-      <c r="D50" s="3"/>
-      <c r="E50" s="3"/>
-    </row>
-    <row r="51" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C51" s="4"/>
-      <c r="D51" s="3"/>
-      <c r="E51" s="3"/>
-    </row>
-    <row r="52" spans="3:5" x14ac:dyDescent="0.35">
-      <c r="C52" s="4"/>
-      <c r="D52" s="3"/>
-      <c r="E52" s="3"/>
-    </row>
-    <row r="53" spans="3:5" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>123</v>
+      </c>
+      <c r="B48" t="s">
+        <v>53</v>
+      </c>
+      <c r="C48" s="2">
+        <v>46257</v>
+      </c>
+      <c r="D48" s="3">
+        <v>0.47916666666666669</v>
+      </c>
+      <c r="E48" s="3">
+        <v>0.49722222222222223</v>
+      </c>
+      <c r="F48" s="6">
+        <v>67.550299999999993</v>
+      </c>
+      <c r="G48" s="6">
+        <v>15.625999999999999</v>
+      </c>
+      <c r="H48" s="6">
+        <v>67.550299999999993</v>
+      </c>
+      <c r="I48" s="6">
+        <v>15.625999999999999</v>
+      </c>
+      <c r="J48" s="6">
+        <v>3</v>
+      </c>
+      <c r="O48" t="s">
+        <v>55</v>
+      </c>
+      <c r="P48" s="6">
+        <v>198</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>38</v>
+      </c>
+      <c r="R48" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="49" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>54</v>
+      </c>
+      <c r="B49" t="s">
+        <v>53</v>
+      </c>
+      <c r="C49" s="2">
+        <v>46257</v>
+      </c>
+      <c r="D49" s="3">
+        <v>0.51388888888888884</v>
+      </c>
+      <c r="E49" s="3">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="F49" s="6">
+        <v>67.5792</v>
+      </c>
+      <c r="G49" s="6">
+        <v>15.7844</v>
+      </c>
+      <c r="H49" s="7">
+        <v>67.5792</v>
+      </c>
+      <c r="I49" s="6">
+        <v>15.7844</v>
+      </c>
+      <c r="J49" s="6">
+        <v>3</v>
+      </c>
+      <c r="K49">
+        <v>20</v>
+      </c>
+      <c r="L49">
+        <v>40</v>
+      </c>
+      <c r="M49" s="6">
+        <v>13.3</v>
+      </c>
+      <c r="N49" s="6">
+        <v>23.9</v>
+      </c>
+      <c r="O49" t="s">
+        <v>55</v>
+      </c>
+      <c r="P49" s="6">
+        <v>147</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>38</v>
+      </c>
+      <c r="R49" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="50" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B50" t="s">
+        <v>53</v>
+      </c>
+      <c r="C50" s="2">
+        <v>46259</v>
+      </c>
+      <c r="D50" s="3">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="E50" s="3">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="F50" s="6">
+        <v>67.531400000000005</v>
+      </c>
+      <c r="G50" s="6">
+        <v>15.6182</v>
+      </c>
+      <c r="H50" s="6">
+        <v>67.531400000000005</v>
+      </c>
+      <c r="I50" s="6">
+        <v>15.6182</v>
+      </c>
+      <c r="J50" s="6">
+        <v>2</v>
+      </c>
+      <c r="K50" s="6">
+        <v>30</v>
+      </c>
+      <c r="L50" s="6">
+        <v>60</v>
+      </c>
+      <c r="M50" s="6">
+        <v>13.5</v>
+      </c>
+      <c r="N50" s="6">
+        <v>26.5</v>
+      </c>
+      <c r="O50" t="s">
+        <v>36</v>
+      </c>
+      <c r="P50" s="6">
+        <v>126</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>124</v>
+      </c>
+      <c r="R50" t="s">
+        <v>99</v>
+      </c>
+      <c r="T50" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="51" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>112</v>
+      </c>
+      <c r="B51" t="s">
+        <v>75</v>
+      </c>
+      <c r="C51" s="2">
+        <v>46260</v>
+      </c>
+      <c r="D51" s="3">
+        <v>0.49305555555555558</v>
+      </c>
+      <c r="E51" s="3">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="F51" s="6">
+        <v>67.504000000000005</v>
+      </c>
+      <c r="G51" s="6">
+        <v>15.321400000000001</v>
+      </c>
+      <c r="H51" s="6">
+        <v>67.504000000000005</v>
+      </c>
+      <c r="I51" s="6">
+        <v>15.321400000000001</v>
+      </c>
+      <c r="J51" s="6">
+        <v>3</v>
+      </c>
+      <c r="K51" s="6">
+        <v>40</v>
+      </c>
+      <c r="L51" s="6">
+        <v>140</v>
+      </c>
+      <c r="O51" t="s">
+        <v>37</v>
+      </c>
+      <c r="P51" s="6">
+        <v>149</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>38</v>
+      </c>
+      <c r="R51" t="s">
+        <v>48</v>
+      </c>
+      <c r="T51" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="52" spans="1:20" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>127</v>
+      </c>
+      <c r="B52" t="s">
+        <v>126</v>
+      </c>
+      <c r="C52" s="2">
+        <v>46260</v>
+      </c>
+      <c r="D52" s="3">
+        <v>0.73958333333333337</v>
+      </c>
+      <c r="E52" s="3">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="F52" s="6">
+        <v>67.533199999999994</v>
+      </c>
+      <c r="G52" s="6">
+        <v>15.118499999999999</v>
+      </c>
+      <c r="H52" s="6">
+        <v>67.533199999999994</v>
+      </c>
+      <c r="I52" s="6">
+        <v>15.118499999999999</v>
+      </c>
+      <c r="J52" s="6">
+        <v>3</v>
+      </c>
+      <c r="K52" s="6">
+        <v>20</v>
+      </c>
+      <c r="L52" s="6">
+        <v>45</v>
+      </c>
+      <c r="O52" t="s">
+        <v>55</v>
+      </c>
+      <c r="P52" s="6">
+        <v>108</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>38</v>
+      </c>
+      <c r="R52" t="s">
+        <v>48</v>
+      </c>
+      <c r="T52" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="53" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C53" s="4"/>
       <c r="D53" s="3"/>
       <c r="E53" s="3"/>
     </row>
-    <row r="54" spans="3:5" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C54" s="4"/>
       <c r="D54" s="3"/>
       <c r="E54" s="3"/>
     </row>
-    <row r="55" spans="3:5" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C55" s="4"/>
       <c r="D55" s="3"/>
       <c r="E55" s="3"/>
     </row>
-    <row r="56" spans="3:5" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C56" s="4"/>
       <c r="D56" s="3"/>
       <c r="E56" s="3"/>
     </row>
-    <row r="57" spans="3:5" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C57" s="4"/>
       <c r="D57" s="3"/>
       <c r="E57" s="3"/>
     </row>
-    <row r="58" spans="3:5" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C58" s="4"/>
       <c r="D58" s="3"/>
       <c r="E58" s="3"/>
     </row>
-    <row r="59" spans="3:5" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C59" s="4"/>
       <c r="D59" s="3"/>
       <c r="E59" s="3"/>
     </row>
-    <row r="60" spans="3:5" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C60" s="4"/>
       <c r="D60" s="3"/>
       <c r="E60" s="3"/>
     </row>
-    <row r="61" spans="3:5" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C61" s="4"/>
       <c r="D61" s="3"/>
       <c r="E61" s="3"/>
     </row>
-    <row r="62" spans="3:5" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C62" s="4"/>
       <c r="D62" s="3"/>
       <c r="E62" s="3"/>
     </row>
-    <row r="63" spans="3:5" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C63" s="4"/>
       <c r="D63" s="3"/>
       <c r="E63" s="3"/>
     </row>
-    <row r="64" spans="3:5" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:20" x14ac:dyDescent="0.35">
       <c r="C64" s="4"/>
       <c r="D64" s="3"/>
       <c r="E64" s="3"/>

--- a/Survey_data_real.xlsx
+++ b/Survey_data_real.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop (1)\Other\ShinyAPPnorway\ACCESS-FjordAPP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{734DDD04-CCB8-47BC-B11D-362EF8DBCC84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55B8E29A-375B-47D9-AFB9-1A8952A2FA01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
     <sheet name="stratum_info" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">catchdata!$A$1:$J$118</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">catchdata!$A$1:$J$180</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">station_info!$A$1:$S$216</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -4689,7 +4689,7 @@
         <v>54</v>
       </c>
       <c r="C165" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D165" t="s">
         <v>96</v>
